--- a/data/source/weekly/cs-en-us-052pct.xlsx
+++ b/data/source/weekly/cs-en-us-052pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -564,7 +564,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -869,8 +869,8 @@
       <c r="H14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>20</v>
@@ -878,260 +878,260 @@
       <c r="K14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="M14" s="14">
-        <v>-100</v>
-      </c>
-      <c r="N14" s="14">
-        <v>-100</v>
+      <c r="L14" s="15">
+        <v>0</v>
+      </c>
+      <c r="M14" s="15">
+        <v>0</v>
+      </c>
+      <c r="N14" s="15">
+        <v>-80</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="15">
+      <c r="E15" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="14">
         <v>3</v>
       </c>
-      <c r="E15" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F15" s="15">
-        <v>3</v>
-      </c>
-      <c r="G15" s="15">
-        <v>6</v>
-      </c>
-      <c r="H15" s="14">
-        <v>-50</v>
-      </c>
-      <c r="I15" s="15">
-        <v>3</v>
-      </c>
-      <c r="J15" s="15">
-        <v>8</v>
-      </c>
-      <c r="K15" s="14">
-        <v>-62.5</v>
-      </c>
-      <c r="L15" s="14">
-        <v>-62.5</v>
-      </c>
-      <c r="M15" s="14">
-        <v>50</v>
-      </c>
-      <c r="N15" s="14">
-        <v>0</v>
+      <c r="G15" s="14">
+        <v>7</v>
+      </c>
+      <c r="H15" s="15">
+        <v>-57.142857142857</v>
+      </c>
+      <c r="I15" s="14">
+        <v>4</v>
+      </c>
+      <c r="J15" s="14">
+        <v>9</v>
+      </c>
+      <c r="K15" s="15">
+        <v>-55.555555555555</v>
+      </c>
+      <c r="L15" s="15">
+        <v>-55.555555555555</v>
+      </c>
+      <c r="M15" s="15">
+        <v>100</v>
+      </c>
+      <c r="N15" s="15">
+        <v>-20</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>13</v>
-      </c>
-      <c r="D16" s="15">
-        <v>12</v>
-      </c>
-      <c r="E16" s="14">
-        <v>8.333333333333</v>
-      </c>
-      <c r="F16" s="15">
-        <v>43</v>
-      </c>
-      <c r="G16" s="15">
+      <c r="C16" s="14">
+        <v>6</v>
+      </c>
+      <c r="D16" s="14">
+        <v>5</v>
+      </c>
+      <c r="E16" s="15">
+        <v>20</v>
+      </c>
+      <c r="F16" s="14">
+        <v>35</v>
+      </c>
+      <c r="G16" s="14">
         <v>27</v>
       </c>
-      <c r="H16" s="14">
-        <v>59.259259259259</v>
-      </c>
-      <c r="I16" s="15">
-        <v>51</v>
-      </c>
-      <c r="J16" s="15">
-        <v>37</v>
-      </c>
-      <c r="K16" s="14">
-        <v>37.837837837837</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-22.727272727272</v>
-      </c>
-      <c r="M16" s="14">
-        <v>-3.773584905660</v>
-      </c>
-      <c r="N16" s="14">
-        <v>-71.508379888268</v>
+      <c r="H16" s="15">
+        <v>29.629629629629</v>
+      </c>
+      <c r="I16" s="14">
+        <v>57</v>
+      </c>
+      <c r="J16" s="14">
+        <v>42</v>
+      </c>
+      <c r="K16" s="15">
+        <v>35.714285714285</v>
+      </c>
+      <c r="L16" s="15">
+        <v>-19.718309859154</v>
+      </c>
+      <c r="M16" s="15">
+        <v>-5</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-73.113207547169</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>14</v>
-      </c>
-      <c r="D17" s="15">
-        <v>17</v>
-      </c>
-      <c r="E17" s="14">
-        <v>-17.647058823529</v>
-      </c>
-      <c r="F17" s="15">
-        <v>59</v>
-      </c>
-      <c r="G17" s="15">
-        <v>62</v>
-      </c>
-      <c r="H17" s="14">
-        <v>-4.838709677419</v>
-      </c>
-      <c r="I17" s="15">
-        <v>83</v>
-      </c>
-      <c r="J17" s="15">
-        <v>80</v>
-      </c>
-      <c r="K17" s="14">
-        <v>3.75</v>
-      </c>
-      <c r="L17" s="14">
-        <v>38.333333333333</v>
-      </c>
-      <c r="M17" s="14">
-        <v>80.434782608695</v>
-      </c>
-      <c r="N17" s="14">
-        <v>9.210526315789</v>
+      <c r="C17" s="14">
+        <v>25</v>
+      </c>
+      <c r="D17" s="14">
+        <v>13</v>
+      </c>
+      <c r="E17" s="15">
+        <v>92.307692307692</v>
+      </c>
+      <c r="F17" s="14">
+        <v>72</v>
+      </c>
+      <c r="G17" s="14">
+        <v>60</v>
+      </c>
+      <c r="H17" s="15">
+        <v>20</v>
+      </c>
+      <c r="I17" s="14">
+        <v>109</v>
+      </c>
+      <c r="J17" s="14">
+        <v>93</v>
+      </c>
+      <c r="K17" s="15">
+        <v>17.204301075268</v>
+      </c>
+      <c r="L17" s="15">
+        <v>37.974683544303</v>
+      </c>
+      <c r="M17" s="15">
+        <v>98.181818181818</v>
+      </c>
+      <c r="N17" s="15">
+        <v>21.111111111111</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>3</v>
-      </c>
-      <c r="D18" s="15">
-        <v>6</v>
-      </c>
-      <c r="E18" s="14">
-        <v>-50</v>
-      </c>
-      <c r="F18" s="15">
-        <v>11</v>
-      </c>
-      <c r="G18" s="15">
-        <v>18</v>
-      </c>
-      <c r="H18" s="14">
-        <v>-38.888888888888</v>
-      </c>
-      <c r="I18" s="15">
-        <v>17</v>
-      </c>
-      <c r="J18" s="15">
-        <v>23</v>
-      </c>
-      <c r="K18" s="14">
-        <v>-26.086956521739</v>
-      </c>
-      <c r="L18" s="14">
-        <v>-19.047619047619</v>
-      </c>
-      <c r="M18" s="14">
-        <v>-64.583333333333</v>
-      </c>
-      <c r="N18" s="14">
-        <v>-92.672413793103</v>
+      <c r="C18" s="14">
+        <v>2</v>
+      </c>
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>100</v>
+      </c>
+      <c r="F18" s="14">
+        <v>9</v>
+      </c>
+      <c r="G18" s="14">
+        <v>10</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-10</v>
+      </c>
+      <c r="I18" s="14">
+        <v>19</v>
+      </c>
+      <c r="J18" s="14">
+        <v>24</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-20.833333333333</v>
+      </c>
+      <c r="L18" s="15">
+        <v>-34.482758620689</v>
+      </c>
+      <c r="M18" s="15">
+        <v>-62.745098039215</v>
+      </c>
+      <c r="N18" s="15">
+        <v>-93.014705882352</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="14">
         <v>17</v>
       </c>
-      <c r="D19" s="15">
-        <v>18</v>
-      </c>
-      <c r="E19" s="14">
-        <v>-5.555555555555</v>
-      </c>
-      <c r="F19" s="15">
-        <v>56</v>
-      </c>
-      <c r="G19" s="15">
-        <v>70</v>
-      </c>
-      <c r="H19" s="14">
-        <v>-20</v>
-      </c>
-      <c r="I19" s="15">
-        <v>77</v>
-      </c>
-      <c r="J19" s="15">
-        <v>90</v>
-      </c>
-      <c r="K19" s="14">
-        <v>-14.444444444444</v>
-      </c>
-      <c r="L19" s="14">
-        <v>-11.494252873563</v>
-      </c>
-      <c r="M19" s="14">
-        <v>48.076923076923</v>
-      </c>
-      <c r="N19" s="14">
-        <v>-22.222222222222</v>
+      <c r="D19" s="14">
+        <v>15</v>
+      </c>
+      <c r="E19" s="15">
+        <v>13.333333333333</v>
+      </c>
+      <c r="F19" s="14">
+        <v>62</v>
+      </c>
+      <c r="G19" s="14">
+        <v>69</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-10.144927536231</v>
+      </c>
+      <c r="I19" s="14">
+        <v>96</v>
+      </c>
+      <c r="J19" s="14">
+        <v>105</v>
+      </c>
+      <c r="K19" s="15">
+        <v>-8.571428571428</v>
+      </c>
+      <c r="L19" s="15">
+        <v>2.127659574468</v>
+      </c>
+      <c r="M19" s="15">
+        <v>54.838709677419</v>
+      </c>
+      <c r="N19" s="15">
+        <v>-11.111111111111</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>1</v>
-      </c>
-      <c r="D20" s="15">
-        <v>5</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-80</v>
-      </c>
-      <c r="F20" s="15">
-        <v>15</v>
-      </c>
-      <c r="G20" s="15">
-        <v>13</v>
-      </c>
-      <c r="H20" s="14">
-        <v>15.384615384615</v>
-      </c>
-      <c r="I20" s="15">
-        <v>18</v>
-      </c>
-      <c r="J20" s="15">
-        <v>23</v>
-      </c>
-      <c r="K20" s="14">
-        <v>-21.739130434782</v>
-      </c>
-      <c r="L20" s="14">
-        <v>-64.705882352941</v>
-      </c>
-      <c r="M20" s="14">
-        <v>0</v>
-      </c>
-      <c r="N20" s="14">
-        <v>-89.156626506024</v>
+      <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="14">
+        <v>8</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-75</v>
+      </c>
+      <c r="F20" s="14">
+        <v>10</v>
+      </c>
+      <c r="G20" s="14">
+        <v>17</v>
+      </c>
+      <c r="H20" s="15">
+        <v>-41.176470588235</v>
+      </c>
+      <c r="I20" s="14">
+        <v>19</v>
+      </c>
+      <c r="J20" s="14">
+        <v>31</v>
+      </c>
+      <c r="K20" s="15">
+        <v>-38.709677419354</v>
+      </c>
+      <c r="L20" s="15">
+        <v>-68.852459016393</v>
+      </c>
+      <c r="M20" s="15">
+        <v>-5</v>
+      </c>
+      <c r="N20" s="15">
+        <v>-90.155440414507</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,77 +1139,77 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D21" s="17">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="E21" s="18">
-        <v>-19.672131147541</v>
+        <v>20.930232558139</v>
       </c>
       <c r="F21" s="17">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="G21" s="17">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H21" s="18">
-        <v>-4.591836734693</v>
+        <v>1.052631578947</v>
       </c>
       <c r="I21" s="17">
-        <v>249</v>
+        <v>305</v>
       </c>
       <c r="J21" s="17">
-        <v>261</v>
+        <v>304</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.597701149425</v>
+        <v>0.328947368421</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.017064846416</v>
+        <v>-11.337209302325</v>
       </c>
       <c r="M21" s="18">
-        <v>13.181818181818</v>
+        <v>21.513944223107</v>
       </c>
       <c r="N21" s="18">
-        <v>-67.236842105263</v>
+        <v>-65.536723163841</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
-      </c>
-      <c r="D22" s="15">
-        <v>2</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-50</v>
-      </c>
-      <c r="F22" s="15">
-        <v>6</v>
-      </c>
-      <c r="G22" s="15">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
+        <v>3</v>
+      </c>
+      <c r="G22" s="14">
         <v>4</v>
       </c>
-      <c r="H22" s="14">
-        <v>50</v>
-      </c>
-      <c r="I22" s="15">
+      <c r="H22" s="15">
+        <v>-25</v>
+      </c>
+      <c r="I22" s="14">
         <v>8</v>
       </c>
-      <c r="J22" s="15">
+      <c r="J22" s="14">
         <v>5</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="15">
         <v>60</v>
       </c>
-      <c r="L22" s="14">
-        <v>60</v>
-      </c>
-      <c r="M22" s="14">
+      <c r="L22" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="M22" s="15">
         <v>700</v>
       </c>
       <c r="N22" s="13" t="s">
@@ -1220,27 +1220,27 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="15">
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" s="14">
         <v>3</v>
       </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I23" s="15">
-        <v>3</v>
-      </c>
       <c r="J23" s="13" t="s">
         <v>20</v>
       </c>
@@ -1250,8 +1250,8 @@
       <c r="L23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M23" s="13" t="s">
-        <v>21</v>
+      <c r="M23" s="15">
+        <v>200</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1261,38 +1261,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
-        <v>28</v>
-      </c>
-      <c r="D24" s="15">
-        <v>24</v>
-      </c>
-      <c r="E24" s="14">
-        <v>16.666666666666</v>
-      </c>
-      <c r="F24" s="15">
-        <v>112</v>
-      </c>
-      <c r="G24" s="15">
-        <v>111</v>
-      </c>
-      <c r="H24" s="14">
-        <v>0.900900900900</v>
-      </c>
-      <c r="I24" s="15">
-        <v>173</v>
-      </c>
-      <c r="J24" s="15">
-        <v>176</v>
-      </c>
-      <c r="K24" s="14">
-        <v>-1.704545454545</v>
-      </c>
-      <c r="L24" s="14">
-        <v>-31.349206349206</v>
-      </c>
-      <c r="M24" s="14">
-        <v>19.310344827586</v>
+      <c r="C24" s="14">
+        <v>45</v>
+      </c>
+      <c r="D24" s="14">
+        <v>35</v>
+      </c>
+      <c r="E24" s="15">
+        <v>28.571428571428</v>
+      </c>
+      <c r="F24" s="14">
+        <v>134</v>
+      </c>
+      <c r="G24" s="14">
+        <v>120</v>
+      </c>
+      <c r="H24" s="15">
+        <v>11.666666666666</v>
+      </c>
+      <c r="I24" s="14">
+        <v>218</v>
+      </c>
+      <c r="J24" s="14">
+        <v>211</v>
+      </c>
+      <c r="K24" s="15">
+        <v>3.317535545023</v>
+      </c>
+      <c r="L24" s="15">
+        <v>-23.508771929824</v>
+      </c>
+      <c r="M24" s="15">
+        <v>29.761904761904</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>16</v>
-      </c>
-      <c r="D25" s="15">
+      <c r="C25" s="14">
+        <v>30</v>
+      </c>
+      <c r="D25" s="14">
         <v>11</v>
       </c>
-      <c r="E25" s="14">
-        <v>45.454545454545</v>
-      </c>
-      <c r="F25" s="15">
-        <v>62</v>
-      </c>
-      <c r="G25" s="15">
-        <v>57</v>
-      </c>
-      <c r="H25" s="14">
-        <v>8.771929824561</v>
-      </c>
-      <c r="I25" s="15">
-        <v>97</v>
-      </c>
-      <c r="J25" s="15">
-        <v>92</v>
-      </c>
-      <c r="K25" s="14">
-        <v>5.434782608695</v>
-      </c>
-      <c r="L25" s="14">
-        <v>-44.252873563218</v>
+      <c r="E25" s="15">
+        <v>172.727272727273</v>
+      </c>
+      <c r="F25" s="14">
+        <v>79</v>
+      </c>
+      <c r="G25" s="14">
+        <v>58</v>
+      </c>
+      <c r="H25" s="15">
+        <v>36.206896551724</v>
+      </c>
+      <c r="I25" s="14">
+        <v>127</v>
+      </c>
+      <c r="J25" s="14">
+        <v>103</v>
+      </c>
+      <c r="K25" s="15">
+        <v>23.300970873786</v>
+      </c>
+      <c r="L25" s="15">
+        <v>-33.854166666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1343,38 +1343,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
-        <v>18</v>
-      </c>
-      <c r="D26" s="15">
-        <v>5</v>
-      </c>
-      <c r="E26" s="14">
-        <v>260</v>
-      </c>
-      <c r="F26" s="15">
-        <v>76</v>
-      </c>
-      <c r="G26" s="15">
-        <v>42</v>
-      </c>
-      <c r="H26" s="14">
-        <v>80.952380952380</v>
-      </c>
-      <c r="I26" s="15">
-        <v>103</v>
-      </c>
-      <c r="J26" s="15">
-        <v>61</v>
-      </c>
-      <c r="K26" s="14">
-        <v>68.852459016393</v>
-      </c>
-      <c r="L26" s="14">
-        <v>19.767441860465</v>
-      </c>
-      <c r="M26" s="14">
-        <v>43.055555555555</v>
+      <c r="C26" s="14">
+        <v>14</v>
+      </c>
+      <c r="D26" s="14">
+        <v>14</v>
+      </c>
+      <c r="E26" s="15">
+        <v>0</v>
+      </c>
+      <c r="F26" s="14">
+        <v>79</v>
+      </c>
+      <c r="G26" s="14">
+        <v>43</v>
+      </c>
+      <c r="H26" s="15">
+        <v>83.720930232558</v>
+      </c>
+      <c r="I26" s="14">
+        <v>118</v>
+      </c>
+      <c r="J26" s="14">
+        <v>75</v>
+      </c>
+      <c r="K26" s="15">
+        <v>57.333333333333</v>
+      </c>
+      <c r="L26" s="15">
+        <v>15.686274509803</v>
+      </c>
+      <c r="M26" s="15">
+        <v>45.679012345679</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="15">
+      <c r="E27" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="14">
         <v>3</v>
       </c>
-      <c r="E27" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F27" s="15">
-        <v>3</v>
-      </c>
-      <c r="G27" s="15">
-        <v>6</v>
-      </c>
-      <c r="H27" s="14">
-        <v>-50</v>
-      </c>
-      <c r="I27" s="15">
+      <c r="G27" s="14">
+        <v>7</v>
+      </c>
+      <c r="H27" s="15">
+        <v>-57.142857142857</v>
+      </c>
+      <c r="I27" s="14">
         <v>4</v>
       </c>
-      <c r="J27" s="15">
-        <v>8</v>
-      </c>
-      <c r="K27" s="14">
-        <v>-50</v>
-      </c>
-      <c r="L27" s="14">
-        <v>-69.230769230769</v>
+      <c r="J27" s="14">
+        <v>9</v>
+      </c>
+      <c r="K27" s="15">
+        <v>-55.555555555555</v>
+      </c>
+      <c r="L27" s="15">
+        <v>-71.428571428571</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F28" s="14">
+        <v>8</v>
+      </c>
+      <c r="G28" s="14">
         <v>4</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="15">
-        <v>7</v>
-      </c>
-      <c r="G28" s="15">
-        <v>4</v>
-      </c>
-      <c r="H28" s="14">
-        <v>75</v>
-      </c>
-      <c r="I28" s="15">
-        <v>9</v>
-      </c>
-      <c r="J28" s="15">
-        <v>6</v>
-      </c>
-      <c r="K28" s="14">
-        <v>50</v>
-      </c>
-      <c r="L28" s="14">
-        <v>-18.181818181818</v>
+      <c r="H28" s="15">
+        <v>100</v>
+      </c>
+      <c r="I28" s="14">
+        <v>10</v>
+      </c>
+      <c r="J28" s="14">
+        <v>8</v>
+      </c>
+      <c r="K28" s="15">
+        <v>25</v>
+      </c>
+      <c r="L28" s="15">
+        <v>-23.076923076923</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,7 +1475,7 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="15">
+      <c r="F29" s="14">
         <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
@@ -1484,22 +1484,22 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="15">
+      <c r="I29" s="14">
         <v>1</v>
       </c>
-      <c r="J29" s="15">
+      <c r="J29" s="14">
         <v>1</v>
       </c>
-      <c r="K29" s="14">
+      <c r="K29" s="15">
         <v>0</v>
       </c>
-      <c r="L29" s="14">
-        <v>-80</v>
-      </c>
-      <c r="M29" s="14">
-        <v>-50</v>
-      </c>
-      <c r="N29" s="14">
+      <c r="L29" s="15">
+        <v>-87.5</v>
+      </c>
+      <c r="M29" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="N29" s="15">
         <v>-85.714285714285</v>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="15">
+      <c r="F30" s="14">
         <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
@@ -1525,22 +1525,22 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="15">
+      <c r="I30" s="14">
         <v>1</v>
       </c>
-      <c r="J30" s="15">
+      <c r="J30" s="14">
         <v>1</v>
       </c>
-      <c r="K30" s="14">
+      <c r="K30" s="15">
         <v>0</v>
       </c>
-      <c r="L30" s="14">
+      <c r="L30" s="15">
+        <v>-75</v>
+      </c>
+      <c r="M30" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="M30" s="14">
-        <v>-50</v>
-      </c>
-      <c r="N30" s="14">
+      <c r="N30" s="15">
         <v>-83.333333333333</v>
       </c>
     </row>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1566,8 +1566,8 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="14">
+        <v>1</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1634,7 +1634,7 @@
       <c r="K33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="14">
+      <c r="L33" s="15">
         <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
@@ -1742,31 +1742,31 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>38</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>43</v>
       </c>
-      <c r="G39" s="15">
-        <v>20</v>
-      </c>
-      <c r="I39" s="15">
+      <c r="G39" s="14">
+        <v>20</v>
+      </c>
+      <c r="I39" s="14">
         <v>23</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="14">
         <v>6</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="15">
         <v>-73.913043478260</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="15">
         <v>-70</v>
       </c>
-      <c r="M39" s="14">
+      <c r="M39" s="15">
         <v>-86.046511627907</v>
       </c>
-      <c r="N39" s="14">
+      <c r="N39" s="15">
         <v>-84.210526315789</v>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="14">
         <v>51</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>60</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>60</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <v>53</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>51</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="15">
         <v>-3.773584905660</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>-15</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>-15</v>
       </c>
-      <c r="N40" s="14">
+      <c r="N40" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>1883</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>1727</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>871</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>603</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>513</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-14.925373134328</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-41.102181400688</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>-70.295309785755</v>
       </c>
-      <c r="N41" s="14">
+      <c r="N41" s="15">
         <v>-72.756240042485</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>848</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>627</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>541</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <v>524</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>937</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>78.816793893129</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>73.197781885397</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>49.441786283891</v>
       </c>
-      <c r="N42" s="14">
+      <c r="N42" s="15">
         <v>10.495283018867</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>2623</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>2344</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>1102</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>766</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>226</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-70.496083550913</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-79.491833030853</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-90.358361774744</v>
       </c>
-      <c r="N43" s="14">
+      <c r="N43" s="15">
         <v>-91.383911551658</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>1157</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>922</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>582</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>528</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>898</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>70.075757575757</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>54.295532646048</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>-2.603036876355</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="15">
         <v>-22.385479688850</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>2467</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>1464</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>626</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>555</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>326</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="15">
         <v>-41.261261261261</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="15">
         <v>-47.923322683706</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="15">
         <v>-77.732240437158</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="15">
         <v>-86.785569517632</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-052pct.xlsx
+++ b/data/source/weekly/cs-en-us-052pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -885,48 +885,48 @@
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-80</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>2</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" s="15">
-        <v>-100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H15" s="15">
-        <v>-57.142857142857</v>
+        <v>-60</v>
       </c>
       <c r="I15" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J15" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K15" s="15">
-        <v>-55.555555555555</v>
+        <v>-50</v>
       </c>
       <c r="L15" s="15">
-        <v>-55.555555555555</v>
+        <v>-40</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N15" s="15">
-        <v>-20</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="F16" s="14">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G16" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H16" s="15">
-        <v>29.629629629629</v>
+        <v>20.833333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="J16" s="14">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K16" s="15">
-        <v>35.714285714285</v>
+        <v>39.130434782608</v>
       </c>
       <c r="L16" s="15">
-        <v>-19.718309859154</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="M16" s="15">
-        <v>-5</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="N16" s="15">
-        <v>-73.113207547169</v>
+        <v>-72.649572649572</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D17" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15">
-        <v>92.307692307692</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G17" s="14">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H17" s="15">
-        <v>20</v>
+        <v>9.677419354838</v>
       </c>
       <c r="I17" s="14">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="J17" s="14">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="K17" s="15">
-        <v>17.204301075268</v>
+        <v>16.190476190476</v>
       </c>
       <c r="L17" s="15">
-        <v>37.974683544303</v>
+        <v>32.608695652173</v>
       </c>
       <c r="M17" s="15">
-        <v>98.181818181818</v>
+        <v>84.848484848484</v>
       </c>
       <c r="N17" s="15">
-        <v>21.111111111111</v>
+        <v>18.446601941747</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>-10</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I18" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J18" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K18" s="15">
-        <v>-20.833333333333</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="L18" s="15">
-        <v>-34.482758620689</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M18" s="15">
-        <v>-62.745098039215</v>
+        <v>-62.5</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.014705882352</v>
+        <v>-93.538461538461</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D19" s="14">
         <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>13.333333333333</v>
+        <v>46.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G19" s="14">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H19" s="15">
-        <v>-10.144927536231</v>
+        <v>1.492537313432</v>
       </c>
       <c r="I19" s="14">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="J19" s="14">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="K19" s="15">
-        <v>-8.571428571428</v>
+        <v>-1.666666666666</v>
       </c>
       <c r="L19" s="15">
-        <v>2.127659574468</v>
+        <v>9.259259259259</v>
       </c>
       <c r="M19" s="15">
-        <v>54.838709677419</v>
+        <v>63.888888888888</v>
       </c>
       <c r="N19" s="15">
-        <v>-11.111111111111</v>
+        <v>-4.065040650406</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G20" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H20" s="15">
-        <v>-41.176470588235</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="I20" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J20" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K20" s="15">
-        <v>-38.709677419354</v>
+        <v>-34.285714285714</v>
       </c>
       <c r="L20" s="15">
-        <v>-68.852459016393</v>
+        <v>-64.615384615384</v>
       </c>
       <c r="M20" s="15">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.155440414507</v>
+        <v>-89.686098654708</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D21" s="17">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E21" s="18">
-        <v>20.930232558139</v>
+        <v>17.5</v>
       </c>
       <c r="F21" s="17">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G21" s="17">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H21" s="18">
-        <v>1.052631578947</v>
+        <v>-2.072538860103</v>
       </c>
       <c r="I21" s="17">
-        <v>305</v>
+        <v>355</v>
       </c>
       <c r="J21" s="17">
-        <v>304</v>
+        <v>344</v>
       </c>
       <c r="K21" s="18">
-        <v>0.328947368421</v>
+        <v>3.197674418604</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.337209302325</v>
+        <v>-9.669211195928</v>
       </c>
       <c r="M21" s="18">
-        <v>21.513944223107</v>
+        <v>22.413793103448</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.536723163841</v>
+        <v>-65.161923454367</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>0</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="14">
         <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K22" s="15">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L22" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="M22" s="15">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1251,7 +1251,7 @@
         <v>21</v>
       </c>
       <c r="M23" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D24" s="14">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E24" s="15">
-        <v>28.571428571428</v>
+        <v>17.241379310344</v>
       </c>
       <c r="F24" s="14">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G24" s="14">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H24" s="15">
-        <v>11.666666666666</v>
+        <v>10.655737704918</v>
       </c>
       <c r="I24" s="14">
-        <v>218</v>
+        <v>252</v>
       </c>
       <c r="J24" s="14">
-        <v>211</v>
+        <v>240</v>
       </c>
       <c r="K24" s="15">
-        <v>3.317535545023</v>
+        <v>5</v>
       </c>
       <c r="L24" s="15">
-        <v>-23.508771929824</v>
+        <v>-18.709677419354</v>
       </c>
       <c r="M24" s="15">
-        <v>29.761904761904</v>
+        <v>30.569948186528</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D25" s="14">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E25" s="15">
-        <v>172.727272727273</v>
+        <v>11.764705882352</v>
       </c>
       <c r="F25" s="14">
         <v>79</v>
       </c>
       <c r="G25" s="14">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H25" s="15">
-        <v>36.206896551724</v>
+        <v>31.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="J25" s="14">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="K25" s="15">
-        <v>23.300970873786</v>
+        <v>22.5</v>
       </c>
       <c r="L25" s="15">
-        <v>-33.854166666666</v>
+        <v>-28.292682926829</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D26" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>23.529411764705</v>
       </c>
       <c r="F26" s="14">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="G26" s="14">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="H26" s="15">
-        <v>83.720930232558</v>
+        <v>50</v>
       </c>
       <c r="I26" s="14">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="J26" s="14">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="K26" s="15">
-        <v>57.333333333333</v>
+        <v>51.086956521739</v>
       </c>
       <c r="L26" s="15">
-        <v>15.686274509803</v>
+        <v>12.096774193548</v>
       </c>
       <c r="M26" s="15">
-        <v>45.679012345679</v>
+        <v>46.315789473684</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>3</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
+        <v>10</v>
+      </c>
+      <c r="H27" s="15">
+        <v>-50</v>
+      </c>
+      <c r="I27" s="14">
         <v>7</v>
       </c>
-      <c r="H27" s="15">
-        <v>-57.142857142857</v>
-      </c>
-      <c r="I27" s="14">
-        <v>4</v>
-      </c>
       <c r="J27" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>-55.555555555555</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>-71.428571428571</v>
+        <v>-56.25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-50</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I28" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J28" s="14">
         <v>8</v>
       </c>
       <c r="K28" s="15">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="L28" s="15">
-        <v>-23.076923076923</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-85.714285714285</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,15 +1541,15 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-052pct.xlsx
+++ b/data/source/weekly/cs-en-us-052pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
         <v>4</v>
       </c>
       <c r="G15" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H15" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K15" s="15">
-        <v>-50</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="L15" s="15">
-        <v>-40</v>
+        <v>-30</v>
       </c>
       <c r="M15" s="15">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="N15" s="15">
-        <v>20</v>
+        <v>16.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F16" s="14">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G16" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H16" s="15">
-        <v>20.833333333333</v>
+        <v>34.615384615384</v>
       </c>
       <c r="I16" s="14">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="J16" s="14">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="K16" s="15">
-        <v>39.130434782608</v>
+        <v>43.137254901960</v>
       </c>
       <c r="L16" s="15">
-        <v>-23.809523809523</v>
+        <v>-25.510204081632</v>
       </c>
       <c r="M16" s="15">
-        <v>-8.571428571428</v>
+        <v>1.388888888888</v>
       </c>
       <c r="N16" s="15">
-        <v>-72.649572649572</v>
+        <v>-72.137404580152</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D17" s="14">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E17" s="15">
-        <v>-8.333333333333</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="F17" s="14">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G17" s="14">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H17" s="15">
-        <v>9.677419354838</v>
+        <v>18.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="J17" s="14">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="K17" s="15">
-        <v>16.190476190476</v>
+        <v>13.821138211382</v>
       </c>
       <c r="L17" s="15">
-        <v>32.608695652173</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M17" s="15">
-        <v>84.848484848484</v>
+        <v>105.882352941176</v>
       </c>
       <c r="N17" s="15">
-        <v>18.446601941747</v>
+        <v>26.126126126126</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>-27.272727272727</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="I18" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J18" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K18" s="15">
-        <v>-19.230769230769</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="L18" s="15">
-        <v>-36.363636363636</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="M18" s="15">
-        <v>-62.5</v>
+        <v>-64.516129032258</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.538461538461</v>
+        <v>-93.905817174515</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,13 +1057,13 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E19" s="15">
-        <v>46.666666666666</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="F19" s="14">
         <v>68</v>
@@ -1075,22 +1075,22 @@
         <v>1.492537313432</v>
       </c>
       <c r="I19" s="14">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="J19" s="14">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="K19" s="15">
-        <v>-1.666666666666</v>
+        <v>-7.913669064748</v>
       </c>
       <c r="L19" s="15">
-        <v>9.259259259259</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M19" s="15">
-        <v>63.888888888888</v>
+        <v>56.097560975609</v>
       </c>
       <c r="N19" s="15">
-        <v>-4.065040650406</v>
+        <v>-5.185185185185</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>3</v>
+      </c>
+      <c r="D20" s="14">
+        <v>7</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-57.142857142857</v>
+      </c>
+      <c r="F20" s="14">
+        <v>9</v>
+      </c>
+      <c r="G20" s="14">
+        <v>24</v>
+      </c>
+      <c r="H20" s="15">
+        <v>-62.5</v>
+      </c>
+      <c r="I20" s="14">
+        <v>26</v>
+      </c>
+      <c r="J20" s="14">
+        <v>42</v>
+      </c>
+      <c r="K20" s="15">
+        <v>-38.095238095238</v>
+      </c>
+      <c r="L20" s="15">
+        <v>-62.318840579710</v>
+      </c>
+      <c r="M20" s="15">
         <v>4</v>
       </c>
-      <c r="D20" s="14">
-        <v>4</v>
-      </c>
-      <c r="E20" s="15">
-        <v>0</v>
-      </c>
-      <c r="F20" s="14">
-        <v>11</v>
-      </c>
-      <c r="G20" s="14">
-        <v>19</v>
-      </c>
-      <c r="H20" s="15">
-        <v>-42.105263157894</v>
-      </c>
-      <c r="I20" s="14">
-        <v>23</v>
-      </c>
-      <c r="J20" s="14">
-        <v>35</v>
-      </c>
-      <c r="K20" s="15">
-        <v>-34.285714285714</v>
-      </c>
-      <c r="L20" s="15">
-        <v>-64.615384615384</v>
-      </c>
-      <c r="M20" s="15">
-        <v>0</v>
-      </c>
       <c r="N20" s="15">
-        <v>-89.686098654708</v>
+        <v>-89.763779527559</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,75 +1139,75 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D21" s="17">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="E21" s="18">
-        <v>17.5</v>
+        <v>-20.370370370370</v>
       </c>
       <c r="F21" s="17">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="G21" s="17">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.072538860103</v>
+        <v>-1.515151515151</v>
       </c>
       <c r="I21" s="17">
-        <v>355</v>
+        <v>397</v>
       </c>
       <c r="J21" s="17">
-        <v>344</v>
+        <v>398</v>
       </c>
       <c r="K21" s="18">
-        <v>3.197674418604</v>
+        <v>-0.251256281407</v>
       </c>
       <c r="L21" s="18">
-        <v>-9.669211195928</v>
+        <v>-8.314087759815</v>
       </c>
       <c r="M21" s="18">
-        <v>22.413793103448</v>
+        <v>27.243589743589</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.161923454367</v>
+        <v>-65.022026431718</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="I22" s="14">
         <v>9</v>
       </c>
       <c r="J22" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K22" s="15">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="L22" s="15">
-        <v>50</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M22" s="15">
         <v>800</v>
@@ -1247,8 +1247,8 @@
       <c r="K23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L23" s="13" t="s">
-        <v>21</v>
+      <c r="L23" s="15">
+        <v>200</v>
       </c>
       <c r="M23" s="15">
         <v>50</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D24" s="14">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>17.241379310344</v>
+        <v>57.692307692307</v>
       </c>
       <c r="F24" s="14">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="G24" s="14">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="H24" s="15">
-        <v>10.655737704918</v>
+        <v>29.824561403508</v>
       </c>
       <c r="I24" s="14">
-        <v>252</v>
+        <v>293</v>
       </c>
       <c r="J24" s="14">
-        <v>240</v>
+        <v>266</v>
       </c>
       <c r="K24" s="15">
-        <v>5</v>
+        <v>10.150375939849</v>
       </c>
       <c r="L24" s="15">
-        <v>-18.709677419354</v>
+        <v>-14.076246334310</v>
       </c>
       <c r="M24" s="15">
-        <v>30.569948186528</v>
+        <v>37.558685446009</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D25" s="14">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E25" s="15">
-        <v>11.764705882352</v>
+        <v>81.818181818181</v>
       </c>
       <c r="F25" s="14">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G25" s="14">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H25" s="15">
-        <v>31.666666666666</v>
+        <v>72</v>
       </c>
       <c r="I25" s="14">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="J25" s="14">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="K25" s="15">
-        <v>22.5</v>
+        <v>27.480916030534</v>
       </c>
       <c r="L25" s="15">
-        <v>-28.292682926829</v>
+        <v>-23.394495412844</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D26" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>23.529411764705</v>
+        <v>69.230769230769</v>
       </c>
       <c r="F26" s="14">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G26" s="14">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H26" s="15">
-        <v>50</v>
+        <v>53.061224489795</v>
       </c>
       <c r="I26" s="14">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="J26" s="14">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="K26" s="15">
-        <v>51.086956521739</v>
+        <v>52.380952380952</v>
       </c>
       <c r="L26" s="15">
-        <v>12.096774193548</v>
+        <v>13.475177304964</v>
       </c>
       <c r="M26" s="15">
-        <v>46.315789473684</v>
+        <v>45.454545454545</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
         <v>5</v>
       </c>
       <c r="G27" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H27" s="15">
+        <v>-44.444444444444</v>
+      </c>
+      <c r="I27" s="14">
+        <v>8</v>
+      </c>
+      <c r="J27" s="14">
+        <v>14</v>
+      </c>
+      <c r="K27" s="15">
+        <v>-42.857142857142</v>
+      </c>
+      <c r="L27" s="15">
         <v>-50</v>
-      </c>
-      <c r="I27" s="14">
-        <v>7</v>
-      </c>
-      <c r="J27" s="14">
-        <v>12</v>
-      </c>
-      <c r="K27" s="15">
-        <v>-41.666666666666</v>
-      </c>
-      <c r="L27" s="15">
-        <v>-56.25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>5</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-80</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>166.666666666667</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J28" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>37.5</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L28" s="15">
-        <v>-26.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1494,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-87.5</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="M29" s="15">
         <v>-66.666666666666</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="M30" s="15">
         <v>-66.666666666666</v>

--- a/data/source/weekly/cs-en-us-052pct.xlsx
+++ b/data/source/weekly/cs-en-us-052pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -892,20 +892,20 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H15" s="15">
         <v>-50</v>
@@ -914,19 +914,19 @@
         <v>7</v>
       </c>
       <c r="J15" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K15" s="15">
-        <v>-46.153846153846</v>
+        <v>-50</v>
       </c>
       <c r="L15" s="15">
-        <v>-30</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>250</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>16.666666666666</v>
+        <v>-22.222222222222</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E16" s="15">
-        <v>80</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="F16" s="14">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G16" s="14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H16" s="15">
-        <v>34.615384615384</v>
+        <v>12</v>
       </c>
       <c r="I16" s="14">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J16" s="14">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="K16" s="15">
-        <v>43.137254901960</v>
+        <v>27.419354838709</v>
       </c>
       <c r="L16" s="15">
-        <v>-25.510204081632</v>
+        <v>-24.761904761904</v>
       </c>
       <c r="M16" s="15">
-        <v>1.388888888888</v>
+        <v>3.947368421052</v>
       </c>
       <c r="N16" s="15">
-        <v>-72.137404580152</v>
+        <v>-72.852233676975</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D17" s="14">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E17" s="15">
-        <v>-5.555555555555</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F17" s="14">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G17" s="14">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H17" s="15">
-        <v>18.333333333333</v>
+        <v>28.070175438596</v>
       </c>
       <c r="I17" s="14">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="J17" s="14">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="K17" s="15">
-        <v>13.821138211382</v>
+        <v>15.328467153284</v>
       </c>
       <c r="L17" s="15">
-        <v>33.333333333333</v>
+        <v>25.396825396825</v>
       </c>
       <c r="M17" s="15">
-        <v>105.882352941176</v>
+        <v>105.194805194805</v>
       </c>
       <c r="N17" s="15">
-        <v>26.126126126126</v>
+        <v>29.508196721311</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E18" s="15">
-        <v>-75</v>
+        <v>-90.909090909090</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H18" s="15">
-        <v>-46.153846153846</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J18" s="14">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="K18" s="15">
-        <v>-26.666666666666</v>
+        <v>-41.463414634146</v>
       </c>
       <c r="L18" s="15">
-        <v>-42.105263157894</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M18" s="15">
-        <v>-64.516129032258</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.905817174515</v>
+        <v>-94.044665012407</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E19" s="15">
-        <v>-36.842105263157</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="F19" s="14">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G19" s="14">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H19" s="15">
-        <v>1.492537313432</v>
+        <v>-3.030303030303</v>
       </c>
       <c r="I19" s="14">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="J19" s="14">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="K19" s="15">
-        <v>-7.913669064748</v>
+        <v>-8.974358974358</v>
       </c>
       <c r="L19" s="15">
-        <v>14.285714285714</v>
+        <v>10.9375</v>
       </c>
       <c r="M19" s="15">
-        <v>56.097560975609</v>
+        <v>51.063829787234</v>
       </c>
       <c r="N19" s="15">
-        <v>-5.185185185185</v>
+        <v>-2.739726027397</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
         <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>-57.142857142857</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F20" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G20" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H20" s="15">
-        <v>-62.5</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="I20" s="14">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J20" s="14">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="K20" s="15">
-        <v>-38.095238095238</v>
+        <v>-36.734693877551</v>
       </c>
       <c r="L20" s="15">
-        <v>-62.318840579710</v>
+        <v>-58.108108108108</v>
       </c>
       <c r="M20" s="15">
-        <v>4</v>
+        <v>10.714285714285</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.763779527559</v>
+        <v>-89.347079037800</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D21" s="17">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E21" s="18">
-        <v>-20.370370370370</v>
+        <v>-32.786885245901</v>
       </c>
       <c r="F21" s="17">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="G21" s="17">
         <v>198</v>
       </c>
       <c r="H21" s="18">
-        <v>-1.515151515151</v>
+        <v>-5.050505050505</v>
       </c>
       <c r="I21" s="17">
-        <v>397</v>
+        <v>442</v>
       </c>
       <c r="J21" s="17">
-        <v>398</v>
+        <v>459</v>
       </c>
       <c r="K21" s="18">
-        <v>-0.251256281407</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="L21" s="18">
-        <v>-8.314087759815</v>
+        <v>-9.426229508196</v>
       </c>
       <c r="M21" s="18">
-        <v>27.243589743589</v>
+        <v>25.925925925925</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.022026431718</v>
+        <v>-65.141955835962</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="14">
         <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F22" s="14">
         <v>2</v>
@@ -1198,19 +1198,19 @@
         <v>-60</v>
       </c>
       <c r="I22" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K22" s="15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>28.571428571428</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M22" s="15">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1229,8 +1229,8 @@
       <c r="E23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="14">
-        <v>1</v>
+      <c r="F23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>20</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D24" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>57.692307692307</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F24" s="14">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="G24" s="14">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H24" s="15">
-        <v>29.824561403508</v>
+        <v>35.593220338983</v>
       </c>
       <c r="I24" s="14">
-        <v>293</v>
+        <v>334</v>
       </c>
       <c r="J24" s="14">
-        <v>266</v>
+        <v>294</v>
       </c>
       <c r="K24" s="15">
-        <v>10.150375939849</v>
+        <v>13.605442176870</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.076246334310</v>
+        <v>-12.565445026178</v>
       </c>
       <c r="M24" s="15">
-        <v>37.558685446009</v>
+        <v>40.928270042194</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D25" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>81.818181818181</v>
+        <v>77.777777777777</v>
       </c>
       <c r="F25" s="14">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G25" s="14">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H25" s="15">
-        <v>72</v>
+        <v>85.416666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="J25" s="14">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="K25" s="15">
-        <v>27.480916030534</v>
+        <v>32.857142857142</v>
       </c>
       <c r="L25" s="15">
-        <v>-23.394495412844</v>
+        <v>-21.518987341772</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E26" s="15">
-        <v>69.230769230769</v>
+        <v>78.571428571428</v>
       </c>
       <c r="F26" s="14">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G26" s="14">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="H26" s="15">
-        <v>53.061224489795</v>
+        <v>34.482758620689</v>
       </c>
       <c r="I26" s="14">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="J26" s="14">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="K26" s="15">
-        <v>52.380952380952</v>
+        <v>52.941176470588</v>
       </c>
       <c r="L26" s="15">
-        <v>13.475177304964</v>
+        <v>14.465408805031</v>
       </c>
       <c r="M26" s="15">
-        <v>45.454545454545</v>
+        <v>32.846715328467</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
       <c r="E27" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H27" s="15">
-        <v>-44.444444444444</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I27" s="14">
         <v>8</v>
       </c>
       <c r="J27" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K27" s="15">
-        <v>-42.857142857142</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-80</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I28" s="14">
         <v>12</v>
       </c>
       <c r="J28" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>-7.692307692307</v>
+        <v>-20</v>
       </c>
       <c r="L28" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,30 +1485,30 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29" s="15">
-        <v>-88.888888888888</v>
+        <v>-80</v>
       </c>
       <c r="M29" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-87.5</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,22 +1526,22 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30" s="15">
-        <v>-80</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-85.714285714285</v>
+        <v>-71.428571428571</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-052pct.xlsx
+++ b/data/source/weekly/cs-en-us-052pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -885,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-83.333333333333</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -896,7 +896,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
         <v>-100</v>
@@ -905,28 +905,28 @@
         <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I15" s="14">
         <v>7</v>
       </c>
       <c r="J15" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K15" s="15">
-        <v>-50</v>
+        <v>-56.25</v>
       </c>
       <c r="L15" s="15">
-        <v>-41.666666666666</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="M15" s="15">
         <v>133.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-22.222222222222</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>-54.545454545454</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="F16" s="14">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G16" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H16" s="15">
-        <v>12</v>
+        <v>-17.241379310344</v>
       </c>
       <c r="I16" s="14">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J16" s="14">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K16" s="15">
-        <v>27.419354838709</v>
+        <v>14.084507042253</v>
       </c>
       <c r="L16" s="15">
-        <v>-24.761904761904</v>
+        <v>-28.318584070796</v>
       </c>
       <c r="M16" s="15">
-        <v>3.947368421052</v>
+        <v>-10.989010989011</v>
       </c>
       <c r="N16" s="15">
-        <v>-72.852233676975</v>
+        <v>-73.786407766990</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D17" s="14">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E17" s="15">
-        <v>28.571428571428</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="F17" s="14">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G17" s="14">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="H17" s="15">
-        <v>28.070175438596</v>
+        <v>6.153846153846</v>
       </c>
       <c r="I17" s="14">
+        <v>181</v>
+      </c>
+      <c r="J17" s="14">
         <v>158</v>
       </c>
-      <c r="J17" s="14">
-        <v>137</v>
-      </c>
       <c r="K17" s="15">
-        <v>15.328467153284</v>
+        <v>14.556962025316</v>
       </c>
       <c r="L17" s="15">
-        <v>25.396825396825</v>
+        <v>35.074626865671</v>
       </c>
       <c r="M17" s="15">
-        <v>105.194805194805</v>
+        <v>112.941176470588</v>
       </c>
       <c r="N17" s="15">
-        <v>29.508196721311</v>
+        <v>40.310077519379</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-90.909090909090</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
         <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H18" s="15">
-        <v>-66.666666666666</v>
+        <v>-70</v>
       </c>
       <c r="I18" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J18" s="14">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K18" s="15">
-        <v>-41.463414634146</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="L18" s="15">
-        <v>-42.857142857142</v>
+        <v>-39.534883720930</v>
       </c>
       <c r="M18" s="15">
-        <v>-66.666666666666</v>
+        <v>-65.789473684210</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.044665012407</v>
+        <v>-93.953488372093</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>-29.411764705882</v>
+        <v>27.272727272727</v>
       </c>
       <c r="F19" s="14">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G19" s="14">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H19" s="15">
-        <v>-3.030303030303</v>
+        <v>-3.225806451612</v>
       </c>
       <c r="I19" s="14">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="J19" s="14">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="K19" s="15">
-        <v>-8.974358974358</v>
+        <v>-7.185628742514</v>
       </c>
       <c r="L19" s="15">
-        <v>10.9375</v>
+        <v>8.391608391608</v>
       </c>
       <c r="M19" s="15">
-        <v>51.063829787234</v>
+        <v>44.859813084112</v>
       </c>
       <c r="N19" s="15">
-        <v>-2.739726027397</v>
+        <v>-4.320987654320</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>-28.571428571428</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G20" s="14">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H20" s="15">
-        <v>-46.153846153846</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I20" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J20" s="14">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K20" s="15">
-        <v>-36.734693877551</v>
+        <v>-33.962264150943</v>
       </c>
       <c r="L20" s="15">
-        <v>-58.108108108108</v>
+        <v>-53.947368421052</v>
       </c>
       <c r="M20" s="15">
-        <v>10.714285714285</v>
+        <v>9.375</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.347079037800</v>
+        <v>-88.709677419354</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D21" s="17">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E21" s="18">
-        <v>-32.786885245901</v>
+        <v>-16</v>
       </c>
       <c r="F21" s="17">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="G21" s="17">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.050505050505</v>
+        <v>-13.170731707317</v>
       </c>
       <c r="I21" s="17">
-        <v>442</v>
+        <v>486</v>
       </c>
       <c r="J21" s="17">
-        <v>459</v>
+        <v>509</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.703703703703</v>
+        <v>-4.518664047151</v>
       </c>
       <c r="L21" s="18">
-        <v>-9.426229508196</v>
+        <v>-7.074569789674</v>
       </c>
       <c r="M21" s="18">
-        <v>25.925925925925</v>
+        <v>23.037974683544</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.141955835962</v>
+        <v>-64.290962527553</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-50</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
         <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="I22" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J22" s="14">
         <v>10</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L22" s="15">
-        <v>42.857142857142</v>
+        <v>37.5</v>
       </c>
       <c r="M22" s="15">
-        <v>400</v>
+        <v>266.666666666667</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="D24" s="14">
         <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>42.857142857142</v>
+        <v>89.285714285714</v>
       </c>
       <c r="F24" s="14">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="G24" s="14">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="H24" s="15">
-        <v>35.593220338983</v>
+        <v>51.351351351351</v>
       </c>
       <c r="I24" s="14">
-        <v>334</v>
+        <v>387</v>
       </c>
       <c r="J24" s="14">
-        <v>294</v>
+        <v>322</v>
       </c>
       <c r="K24" s="15">
-        <v>13.605442176870</v>
+        <v>20.186335403726</v>
       </c>
       <c r="L24" s="15">
-        <v>-12.565445026178</v>
+        <v>-7.416267942583</v>
       </c>
       <c r="M24" s="15">
-        <v>40.928270042194</v>
+        <v>56.048387096774</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D25" s="14">
         <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>77.777777777777</v>
+        <v>177.777777777778</v>
       </c>
       <c r="F25" s="14">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G25" s="14">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H25" s="15">
-        <v>85.416666666666</v>
+        <v>80.434782608695</v>
       </c>
       <c r="I25" s="14">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="J25" s="14">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="K25" s="15">
-        <v>32.857142857142</v>
+        <v>41.610738255033</v>
       </c>
       <c r="L25" s="15">
-        <v>-21.518987341772</v>
+        <v>-17.898832684824</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D26" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E26" s="15">
-        <v>78.571428571428</v>
+        <v>18.75</v>
       </c>
       <c r="F26" s="14">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G26" s="14">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H26" s="15">
-        <v>34.482758620689</v>
+        <v>36.666666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="J26" s="14">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="K26" s="15">
-        <v>52.941176470588</v>
+        <v>47.407407407407</v>
       </c>
       <c r="L26" s="15">
-        <v>14.465408805031</v>
+        <v>9.944751381215</v>
       </c>
       <c r="M26" s="15">
-        <v>32.846715328467</v>
+        <v>25.157232704402</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H27" s="15">
-        <v>-42.857142857142</v>
+        <v>-37.5</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K27" s="15">
-        <v>-46.666666666666</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="L27" s="15">
-        <v>-55.555555555555</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>4</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
         <v>9</v>
       </c>
       <c r="H28" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J28" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K28" s="15">
-        <v>-20</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="L28" s="15">
-        <v>-33.333333333333</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1500,15 +1500,15 @@
         <v>-33.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-75</v>
+        <v>-84.615384615384</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-71.428571428571</v>
+        <v>-77.777777777777</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-052pct.xlsx
+++ b/data/source/weekly/cs-en-us-052pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -882,51 +882,51 @@
         <v>0</v>
       </c>
       <c r="M14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="N14" s="15">
-        <v>-90.909090909090</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14">
         <v>2</v>
       </c>
-      <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>3</v>
-      </c>
       <c r="G15" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H15" s="15">
-        <v>-57.142857142857</v>
+        <v>-60</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K15" s="15">
-        <v>-56.25</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="L15" s="15">
-        <v>-46.153846153846</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M15" s="15">
-        <v>133.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="N15" s="15">
-        <v>-30</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>-77.777777777777</v>
+        <v>40</v>
       </c>
       <c r="F16" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G16" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H16" s="15">
-        <v>-17.241379310344</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J16" s="14">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K16" s="15">
-        <v>14.084507042253</v>
+        <v>17.105263157894</v>
       </c>
       <c r="L16" s="15">
-        <v>-28.318584070796</v>
+        <v>-24.576271186440</v>
       </c>
       <c r="M16" s="15">
-        <v>-10.989010989011</v>
+        <v>-11.881188118811</v>
       </c>
       <c r="N16" s="15">
-        <v>-73.786407766990</v>
+        <v>-73.111782477341</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D17" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E17" s="15">
-        <v>-4.761904761904</v>
+        <v>15</v>
       </c>
       <c r="F17" s="14">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="G17" s="14">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="H17" s="15">
-        <v>6.153846153846</v>
+        <v>10.958904109589</v>
       </c>
       <c r="I17" s="14">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="J17" s="14">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="K17" s="15">
-        <v>14.556962025316</v>
+        <v>14.606741573033</v>
       </c>
       <c r="L17" s="15">
-        <v>35.074626865671</v>
+        <v>41.666666666666</v>
       </c>
       <c r="M17" s="15">
-        <v>112.941176470588</v>
+        <v>117.021276595745</v>
       </c>
       <c r="N17" s="15">
-        <v>40.310077519379</v>
+        <v>46.762589928057</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E18" s="15">
+        <v>-62.5</v>
+      </c>
+      <c r="F18" s="14">
+        <v>9</v>
+      </c>
+      <c r="G18" s="14">
+        <v>26</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-65.384615384615</v>
+      </c>
+      <c r="I18" s="14">
+        <v>30</v>
+      </c>
+      <c r="J18" s="14">
+        <v>52</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-42.307692307692</v>
+      </c>
+      <c r="L18" s="15">
         <v>-33.333333333333</v>
       </c>
-      <c r="F18" s="14">
-        <v>6</v>
-      </c>
-      <c r="G18" s="14">
-        <v>20</v>
-      </c>
-      <c r="H18" s="15">
-        <v>-70</v>
-      </c>
-      <c r="I18" s="14">
-        <v>26</v>
-      </c>
-      <c r="J18" s="14">
-        <v>44</v>
-      </c>
-      <c r="K18" s="15">
-        <v>-40.909090909090</v>
-      </c>
-      <c r="L18" s="15">
-        <v>-39.534883720930</v>
-      </c>
       <c r="M18" s="15">
-        <v>-65.789473684210</v>
+        <v>-64.705882352941</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.953488372093</v>
+        <v>-93.723849372384</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E19" s="15">
-        <v>27.272727272727</v>
+        <v>-37.5</v>
       </c>
       <c r="F19" s="14">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G19" s="14">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H19" s="15">
-        <v>-3.225806451612</v>
+        <v>-20.634920634920</v>
       </c>
       <c r="I19" s="14">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="J19" s="14">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="K19" s="15">
-        <v>-7.185628742514</v>
+        <v>-8.743169398907</v>
       </c>
       <c r="L19" s="15">
-        <v>8.391608391608</v>
+        <v>5.031446540880</v>
       </c>
       <c r="M19" s="15">
-        <v>44.859813084112</v>
+        <v>41.525423728813</v>
       </c>
       <c r="N19" s="15">
-        <v>-4.320987654320</v>
+        <v>-3.468208092485</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
         <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G20" s="14">
         <v>22</v>
       </c>
       <c r="H20" s="15">
-        <v>-27.272727272727</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="I20" s="14">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J20" s="14">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K20" s="15">
-        <v>-33.962264150943</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="L20" s="15">
-        <v>-53.947368421052</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M20" s="15">
-        <v>9.375</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.709677419354</v>
+        <v>-87.610619469026</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D21" s="17">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E21" s="18">
-        <v>-16</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="F21" s="17">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="G21" s="17">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.170731707317</v>
+        <v>-15.068493150684</v>
       </c>
       <c r="I21" s="17">
-        <v>486</v>
+        <v>541</v>
       </c>
       <c r="J21" s="17">
-        <v>509</v>
+        <v>563</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.518664047151</v>
+        <v>-3.907637655417</v>
       </c>
       <c r="L21" s="18">
-        <v>-7.074569789674</v>
+        <v>-2.872531418312</v>
       </c>
       <c r="M21" s="18">
-        <v>23.037974683544</v>
+        <v>23.234624145785</v>
       </c>
       <c r="N21" s="18">
-        <v>-64.290962527553</v>
+        <v>-63.544474393531</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,13 +1189,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
         <v>11</v>
@@ -1207,7 +1207,7 @@
         <v>10</v>
       </c>
       <c r="L22" s="15">
-        <v>37.5</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="M22" s="15">
         <v>266.666666666667</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E24" s="15">
-        <v>89.285714285714</v>
+        <v>9.375</v>
       </c>
       <c r="F24" s="14">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G24" s="14">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H24" s="15">
-        <v>51.351351351351</v>
+        <v>46.491228070175</v>
       </c>
       <c r="I24" s="14">
-        <v>387</v>
+        <v>420</v>
       </c>
       <c r="J24" s="14">
-        <v>322</v>
+        <v>354</v>
       </c>
       <c r="K24" s="15">
-        <v>20.186335403726</v>
+        <v>18.644067796610</v>
       </c>
       <c r="L24" s="15">
-        <v>-7.416267942583</v>
+        <v>-4.109589041095</v>
       </c>
       <c r="M24" s="15">
-        <v>56.048387096774</v>
+        <v>53.284671532846</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D25" s="14">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E25" s="15">
-        <v>177.777777777778</v>
+        <v>23.529411764705</v>
       </c>
       <c r="F25" s="14">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G25" s="14">
         <v>46</v>
       </c>
       <c r="H25" s="15">
-        <v>80.434782608695</v>
+        <v>84.782608695652</v>
       </c>
       <c r="I25" s="14">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="J25" s="14">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="K25" s="15">
-        <v>41.610738255033</v>
+        <v>39.759036144578</v>
       </c>
       <c r="L25" s="15">
-        <v>-17.898832684824</v>
+        <v>-11.450381679389</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D26" s="14">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E26" s="15">
-        <v>18.75</v>
+        <v>-25</v>
       </c>
       <c r="F26" s="14">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G26" s="14">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="H26" s="15">
-        <v>36.666666666666</v>
+        <v>17.910447761194</v>
       </c>
       <c r="I26" s="14">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="J26" s="14">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="K26" s="15">
-        <v>47.407407407407</v>
+        <v>36.477987421383</v>
       </c>
       <c r="L26" s="15">
-        <v>9.944751381215</v>
+        <v>10.152284263959</v>
       </c>
       <c r="M26" s="15">
-        <v>25.157232704402</v>
+        <v>25.433526011560</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,31 +1388,31 @@
         <v>1</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
+        <v>0</v>
+      </c>
+      <c r="F27" s="14">
+        <v>3</v>
+      </c>
+      <c r="G27" s="14">
+        <v>6</v>
+      </c>
+      <c r="H27" s="15">
         <v>-50</v>
       </c>
-      <c r="F27" s="14">
-        <v>5</v>
-      </c>
-      <c r="G27" s="14">
-        <v>8</v>
-      </c>
-      <c r="H27" s="15">
-        <v>-37.5</v>
-      </c>
       <c r="I27" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K27" s="15">
-        <v>-47.058823529411</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L27" s="15">
-        <v>-52.631578947368</v>
+        <v>-50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>4</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H28" s="15">
-        <v>-33.333333333333</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="I28" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J28" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K28" s="15">
-        <v>-5.882352941176</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="L28" s="15">
-        <v>-27.272727272727</v>
+        <v>-20</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>0</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
       </c>
       <c r="J29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
         <v>-80</v>
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>0</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
       </c>
       <c r="J30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
         <v>-66.666666666666</v>
@@ -1610,29 +1610,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="14">
+        <v>1</v>
+      </c>
+      <c r="H33" s="15">
+        <v>-100</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>21</v>
+      <c r="J33" s="14">
+        <v>1</v>
+      </c>
+      <c r="K33" s="15">
+        <v>-100</v>
       </c>
       <c r="L33" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-052pct.xlsx
+++ b/data/source/weekly/cs-en-us-052pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>2</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>2</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -870,7 +870,7 @@
         <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>20</v>
@@ -879,36 +879,36 @@
         <v>21</v>
       </c>
       <c r="L14" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M14" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="N14" s="15">
-        <v>-91.666666666666</v>
+        <v>-76.923076923076</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
-      </c>
-      <c r="F15" s="14">
-        <v>2</v>
-      </c>
       <c r="G15" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-60</v>
+        <v>-75</v>
       </c>
       <c r="I15" s="14">
         <v>8</v>
@@ -920,13 +920,13 @@
         <v>-52.941176470588</v>
       </c>
       <c r="L15" s="15">
-        <v>-38.461538461538</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>166.666666666667</v>
+        <v>60</v>
       </c>
       <c r="N15" s="15">
-        <v>-33.333333333333</v>
+        <v>-46.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E16" s="15">
-        <v>40</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G16" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H16" s="15">
-        <v>-16.666666666666</v>
+        <v>-40</v>
       </c>
       <c r="I16" s="14">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="J16" s="14">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K16" s="15">
-        <v>17.105263157894</v>
+        <v>10.465116279069</v>
       </c>
       <c r="L16" s="15">
-        <v>-24.576271186440</v>
+        <v>-22.764227642276</v>
       </c>
       <c r="M16" s="15">
-        <v>-11.881188118811</v>
+        <v>-12.037037037037</v>
       </c>
       <c r="N16" s="15">
-        <v>-73.111782477341</v>
+        <v>-74.114441416893</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D17" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E17" s="15">
-        <v>15</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="F17" s="14">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G17" s="14">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H17" s="15">
-        <v>10.958904109589</v>
+        <v>-1.315789473684</v>
       </c>
       <c r="I17" s="14">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="J17" s="14">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="K17" s="15">
-        <v>14.606741573033</v>
+        <v>8.542713567839</v>
       </c>
       <c r="L17" s="15">
-        <v>41.666666666666</v>
+        <v>41.176470588235</v>
       </c>
       <c r="M17" s="15">
-        <v>117.021276595745</v>
+        <v>113.861386138614</v>
       </c>
       <c r="N17" s="15">
-        <v>46.762589928057</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-62.5</v>
+        <v>-20</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G18" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H18" s="15">
-        <v>-65.384615384615</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I18" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J18" s="14">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K18" s="15">
-        <v>-42.307692307692</v>
+        <v>-38.596491228070</v>
       </c>
       <c r="L18" s="15">
-        <v>-33.333333333333</v>
+        <v>-25.531914893617</v>
       </c>
       <c r="M18" s="15">
-        <v>-64.705882352941</v>
+        <v>-63.541666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.723849372384</v>
+        <v>-93.358633776091</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D19" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>-37.5</v>
+        <v>61.538461538461</v>
       </c>
       <c r="F19" s="14">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G19" s="14">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H19" s="15">
-        <v>-20.634920634920</v>
+        <v>1.754385964912</v>
       </c>
       <c r="I19" s="14">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="J19" s="14">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="K19" s="15">
-        <v>-8.743169398907</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="L19" s="15">
-        <v>5.031446540880</v>
+        <v>8.620689655172</v>
       </c>
       <c r="M19" s="15">
-        <v>41.525423728813</v>
+        <v>53.658536585365</v>
       </c>
       <c r="N19" s="15">
-        <v>-3.468208092485</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>75</v>
+        <v>700</v>
       </c>
       <c r="F20" s="14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G20" s="14">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H20" s="15">
-        <v>-13.636363636363</v>
+        <v>50</v>
       </c>
       <c r="I20" s="14">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="J20" s="14">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K20" s="15">
-        <v>-26.315789473684</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="L20" s="15">
-        <v>-45.454545454545</v>
+        <v>-39.759036144578</v>
       </c>
       <c r="M20" s="15">
-        <v>16.666666666666</v>
+        <v>25</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.610619469026</v>
+        <v>-86.338797814207</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>51</v>
       </c>
       <c r="D21" s="17">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E21" s="18">
-        <v>-5.555555555555</v>
+        <v>2</v>
       </c>
       <c r="F21" s="17">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="G21" s="17">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.068493150684</v>
+        <v>-10.232558139534</v>
       </c>
       <c r="I21" s="17">
-        <v>541</v>
+        <v>596</v>
       </c>
       <c r="J21" s="17">
-        <v>563</v>
+        <v>613</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.907637655417</v>
+        <v>-2.773246329526</v>
       </c>
       <c r="L21" s="18">
-        <v>-2.872531418312</v>
+        <v>0</v>
       </c>
       <c r="M21" s="18">
-        <v>23.234624145785</v>
+        <v>25.473684210526</v>
       </c>
       <c r="N21" s="18">
-        <v>-63.544474393531</v>
+        <v>-63.368162261831</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1192,10 +1192,10 @@
         <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>11</v>
@@ -1207,7 +1207,7 @@
         <v>10</v>
       </c>
       <c r="L22" s="15">
-        <v>-15.384615384615</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="M22" s="15">
         <v>266.666666666667</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D24" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E24" s="15">
-        <v>9.375</v>
+        <v>50</v>
       </c>
       <c r="F24" s="14">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="G24" s="14">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="H24" s="15">
-        <v>46.491228070175</v>
+        <v>41.935483870967</v>
       </c>
       <c r="I24" s="14">
-        <v>420</v>
+        <v>471</v>
       </c>
       <c r="J24" s="14">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="K24" s="15">
-        <v>18.644067796610</v>
+        <v>20.769230769230</v>
       </c>
       <c r="L24" s="15">
-        <v>-4.109589041095</v>
+        <v>-3.680981595092</v>
       </c>
       <c r="M24" s="15">
-        <v>53.284671532846</v>
+        <v>58.053691275167</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D25" s="14">
         <v>17</v>
       </c>
       <c r="E25" s="15">
-        <v>23.529411764705</v>
+        <v>117.647058823529</v>
       </c>
       <c r="F25" s="14">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G25" s="14">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="H25" s="15">
-        <v>84.782608695652</v>
+        <v>92.307692307692</v>
       </c>
       <c r="I25" s="14">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="J25" s="14">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="K25" s="15">
-        <v>39.759036144578</v>
+        <v>47.540983606557</v>
       </c>
       <c r="L25" s="15">
-        <v>-11.450381679389</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E26" s="15">
-        <v>-25</v>
+        <v>-69.565217391304</v>
       </c>
       <c r="F26" s="14">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="G26" s="14">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="H26" s="15">
-        <v>17.910447761194</v>
+        <v>-12.987012987013</v>
       </c>
       <c r="I26" s="14">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="J26" s="14">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="K26" s="15">
-        <v>36.477987421383</v>
+        <v>22.527472527472</v>
       </c>
       <c r="L26" s="15">
-        <v>10.152284263959</v>
+        <v>6.190476190476</v>
       </c>
       <c r="M26" s="15">
-        <v>25.433526011560</v>
+        <v>17.368421052631</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,20 +1384,20 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
         <v>-50</v>
@@ -1412,7 +1412,7 @@
         <v>-44.444444444444</v>
       </c>
       <c r="L27" s="15">
-        <v>-50</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
-      </c>
-      <c r="D28" s="14">
-        <v>4</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G28" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>-30.769230769230</v>
+        <v>37.5</v>
       </c>
       <c r="I28" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J28" s="14">
         <v>21</v>
       </c>
       <c r="K28" s="15">
-        <v>-4.761904761904</v>
+        <v>9.523809523809</v>
       </c>
       <c r="L28" s="15">
-        <v>-20</v>
+        <v>-8</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="14">
+      <c r="C29" s="14">
         <v>1</v>
       </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="14">
         <v>2</v>
       </c>
       <c r="K29" s="15">
+        <v>50</v>
+      </c>
+      <c r="L29" s="15">
+        <v>-70</v>
+      </c>
+      <c r="M29" s="15">
         <v>0</v>
       </c>
-      <c r="L29" s="15">
-        <v>-80</v>
-      </c>
-      <c r="M29" s="15">
-        <v>-33.333333333333</v>
-      </c>
       <c r="N29" s="15">
-        <v>-84.615384615384</v>
+        <v>-78.571428571428</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="14">
+      <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="14">
         <v>2</v>
       </c>
       <c r="K30" s="15">
+        <v>50</v>
+      </c>
+      <c r="L30" s="15">
+        <v>-50</v>
+      </c>
+      <c r="M30" s="15">
         <v>0</v>
       </c>
-      <c r="L30" s="15">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="M30" s="15">
-        <v>-33.333333333333</v>
-      </c>
       <c r="N30" s="15">
-        <v>-77.777777777777</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1620,7 +1620,7 @@
         <v>20</v>
       </c>
       <c r="G33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" s="15">
         <v>-100</v>
@@ -1629,7 +1629,7 @@
         <v>20</v>
       </c>
       <c r="J33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-052pct.xlsx
+++ b/data/source/weekly/cs-en-us-052pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>2</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -885,15 +885,15 @@
         <v>50</v>
       </c>
       <c r="N14" s="15">
-        <v>-76.923076923076</v>
+        <v>-78.571428571428</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-75</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
         <v>17</v>
       </c>
       <c r="K15" s="15">
-        <v>-52.941176470588</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="L15" s="15">
-        <v>-46.666666666666</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="M15" s="15">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N15" s="15">
-        <v>-46.666666666666</v>
+        <v>-47.058823529411</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D16" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F16" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G16" s="14">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H16" s="15">
-        <v>-40</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="I16" s="14">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="J16" s="14">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="K16" s="15">
-        <v>10.465116279069</v>
+        <v>12.903225806451</v>
       </c>
       <c r="L16" s="15">
-        <v>-22.764227642276</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="M16" s="15">
-        <v>-12.037037037037</v>
+        <v>-9.482758620689</v>
       </c>
       <c r="N16" s="15">
-        <v>-74.114441416893</v>
+        <v>-74.009900990099</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D17" s="14">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>-47.619047619047</v>
+        <v>212.5</v>
       </c>
       <c r="F17" s="14">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G17" s="14">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H17" s="15">
-        <v>-1.315789473684</v>
+        <v>15.714285714285</v>
       </c>
       <c r="I17" s="14">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="J17" s="14">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="K17" s="15">
-        <v>8.542713567839</v>
+        <v>16.908212560386</v>
       </c>
       <c r="L17" s="15">
-        <v>41.176470588235</v>
+        <v>48.466257668711</v>
       </c>
       <c r="M17" s="15">
-        <v>113.861386138614</v>
+        <v>130.47619047619</v>
       </c>
       <c r="N17" s="15">
-        <v>44</v>
+        <v>49.382716049382</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>-20</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H18" s="15">
-        <v>-55.555555555555</v>
+        <v>-50</v>
       </c>
       <c r="I18" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J18" s="14">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="K18" s="15">
-        <v>-38.596491228070</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L18" s="15">
-        <v>-25.531914893617</v>
+        <v>-25</v>
       </c>
       <c r="M18" s="15">
-        <v>-63.541666666666</v>
+        <v>-64.705882352941</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.358633776091</v>
+        <v>-93.803786574870</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,13 +1057,13 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E19" s="15">
-        <v>61.538461538461</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="F19" s="14">
         <v>58</v>
@@ -1075,22 +1075,22 @@
         <v>1.754385964912</v>
       </c>
       <c r="I19" s="14">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="J19" s="14">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="K19" s="15">
-        <v>-3.571428571428</v>
+        <v>-5.633802816901</v>
       </c>
       <c r="L19" s="15">
-        <v>8.620689655172</v>
+        <v>1.005025125628</v>
       </c>
       <c r="M19" s="15">
-        <v>53.658536585365</v>
+        <v>51.127819548872</v>
       </c>
       <c r="N19" s="15">
-        <v>0</v>
+        <v>-1.470588235294</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>700</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G20" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H20" s="15">
-        <v>50</v>
+        <v>53.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J20" s="14">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="K20" s="15">
-        <v>-13.793103448275</v>
+        <v>-15.625</v>
       </c>
       <c r="L20" s="15">
-        <v>-39.759036144578</v>
+        <v>-40</v>
       </c>
       <c r="M20" s="15">
-        <v>25</v>
+        <v>22.727272727272</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.338797814207</v>
+        <v>-86.329113924050</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D21" s="17">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E21" s="18">
-        <v>2</v>
+        <v>22.727272727272</v>
       </c>
       <c r="F21" s="17">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="G21" s="17">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="H21" s="18">
-        <v>-10.232558139534</v>
+        <v>2.020202020202</v>
       </c>
       <c r="I21" s="17">
-        <v>596</v>
+        <v>650</v>
       </c>
       <c r="J21" s="17">
-        <v>613</v>
+        <v>657</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.773246329526</v>
+        <v>-1.065449010654</v>
       </c>
       <c r="L21" s="18">
-        <v>0</v>
+        <v>-0.153609831029</v>
       </c>
       <c r="M21" s="18">
-        <v>25.473684210526</v>
+        <v>27.952755905511</v>
       </c>
       <c r="N21" s="18">
-        <v>-63.368162261831</v>
+        <v>-63.421496904895</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,13 +1189,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
-      </c>
-      <c r="G22" s="14">
-        <v>2</v>
-      </c>
-      <c r="H22" s="15">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>11</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E24" s="15">
-        <v>50</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="F24" s="14">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="G24" s="14">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="H24" s="15">
-        <v>41.935483870967</v>
+        <v>22.388059701492</v>
       </c>
       <c r="I24" s="14">
-        <v>471</v>
+        <v>498</v>
       </c>
       <c r="J24" s="14">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="K24" s="15">
-        <v>20.769230769230</v>
+        <v>16.355140186915</v>
       </c>
       <c r="L24" s="15">
-        <v>-3.680981595092</v>
+        <v>-4.780114722753</v>
       </c>
       <c r="M24" s="15">
-        <v>58.053691275167</v>
+        <v>53.703703703703</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D25" s="14">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E25" s="15">
-        <v>117.647058823529</v>
+        <v>20</v>
       </c>
       <c r="F25" s="14">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G25" s="14">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H25" s="15">
-        <v>92.307692307692</v>
+        <v>79.245283018867</v>
       </c>
       <c r="I25" s="14">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="J25" s="14">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="K25" s="15">
-        <v>47.540983606557</v>
+        <v>46.113989637305</v>
       </c>
       <c r="L25" s="15">
-        <v>-9.090909090909</v>
+        <v>-9.615384615384</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D26" s="14">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E26" s="15">
-        <v>-69.565217391304</v>
+        <v>15</v>
       </c>
       <c r="F26" s="14">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G26" s="14">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H26" s="15">
-        <v>-12.987012987013</v>
+        <v>-21.686746987951</v>
       </c>
       <c r="I26" s="14">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="J26" s="14">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="K26" s="15">
-        <v>22.527472527472</v>
+        <v>21.287128712871</v>
       </c>
       <c r="L26" s="15">
-        <v>6.190476190476</v>
+        <v>10.859728506787</v>
       </c>
       <c r="M26" s="15">
-        <v>17.368421052631</v>
+        <v>20.689655172413</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>2</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J27" s="14">
         <v>18</v>
       </c>
       <c r="K27" s="15">
-        <v>-44.444444444444</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>-54.545454545454</v>
+        <v>-50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>4</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-75</v>
       </c>
       <c r="F28" s="14">
         <v>11</v>
       </c>
       <c r="G28" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>37.5</v>
+        <v>10</v>
       </c>
       <c r="I28" s="14">
         <v>23</v>
       </c>
       <c r="J28" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K28" s="15">
-        <v>9.523809523809</v>
+        <v>-8</v>
       </c>
       <c r="L28" s="15">
-        <v>-8</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1467,7 +1467,7 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,31 +1476,31 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I29" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J29" s="14">
         <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="L29" s="15">
-        <v>-70</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="M29" s="15">
         <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-78.571428571428</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1526,22 +1526,22 @@
         <v>100</v>
       </c>
       <c r="I30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" s="14">
         <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M30" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="N30" s="15">
-        <v>-70</v>
+        <v>-63.636363636363</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-052pct.xlsx
+++ b/data/source/weekly/cs-en-us-052pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,38 +895,38 @@
       <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
+        <v>3</v>
+      </c>
+      <c r="G15" s="14">
         <v>2</v>
       </c>
-      <c r="G15" s="14">
-        <v>3</v>
-      </c>
       <c r="H15" s="15">
-        <v>-33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K15" s="15">
-        <v>-47.058823529411</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L15" s="15">
-        <v>-47.058823529411</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="M15" s="15">
-        <v>50</v>
+        <v>42.857142857142</v>
       </c>
       <c r="N15" s="15">
-        <v>-47.058823529411</v>
+        <v>-44.444444444444</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>8</v>
+      </c>
+      <c r="D16" s="14">
         <v>9</v>
       </c>
-      <c r="D16" s="14">
-        <v>7</v>
-      </c>
       <c r="E16" s="15">
-        <v>28.571428571428</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F16" s="14">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G16" s="14">
         <v>31</v>
       </c>
       <c r="H16" s="15">
-        <v>-19.354838709677</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="J16" s="14">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="K16" s="15">
-        <v>12.903225806451</v>
+        <v>10.784313725490</v>
       </c>
       <c r="L16" s="15">
-        <v>-21.052631578947</v>
+        <v>-20.979020979021</v>
       </c>
       <c r="M16" s="15">
-        <v>-9.482758620689</v>
+        <v>-5.042016806722</v>
       </c>
       <c r="N16" s="15">
-        <v>-74.009900990099</v>
+        <v>-73.781902552204</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>212.5</v>
+        <v>128.571428571429</v>
       </c>
       <c r="F17" s="14">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G17" s="14">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="H17" s="15">
-        <v>15.714285714285</v>
+        <v>41.071428571428</v>
       </c>
       <c r="I17" s="14">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="J17" s="14">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="K17" s="15">
-        <v>16.908212560386</v>
+        <v>21.495327102803</v>
       </c>
       <c r="L17" s="15">
-        <v>48.466257668711</v>
+        <v>46.067415730337</v>
       </c>
       <c r="M17" s="15">
-        <v>130.47619047619</v>
+        <v>126.086956521739</v>
       </c>
       <c r="N17" s="15">
-        <v>49.382716049382</v>
+        <v>50.289017341040</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,13 +1016,13 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-83.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
         <v>11</v>
@@ -1034,22 +1034,22 @@
         <v>-50</v>
       </c>
       <c r="I18" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J18" s="14">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K18" s="15">
-        <v>-42.857142857142</v>
+        <v>-42.424242424242</v>
       </c>
       <c r="L18" s="15">
-        <v>-25</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="M18" s="15">
-        <v>-64.705882352941</v>
+        <v>-63.809523809523</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.803786574870</v>
+        <v>-93.831168831168</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>15</v>
+      </c>
+      <c r="D19" s="14">
         <v>14</v>
       </c>
-      <c r="D19" s="14">
-        <v>17</v>
-      </c>
       <c r="E19" s="15">
-        <v>-17.647058823529</v>
+        <v>7.142857142857</v>
       </c>
       <c r="F19" s="14">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G19" s="14">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H19" s="15">
-        <v>1.754385964912</v>
+        <v>-5</v>
       </c>
       <c r="I19" s="14">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="J19" s="14">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="K19" s="15">
-        <v>-5.633802816901</v>
+        <v>-4.845814977973</v>
       </c>
       <c r="L19" s="15">
-        <v>1.005025125628</v>
+        <v>3.846153846153</v>
       </c>
       <c r="M19" s="15">
-        <v>51.127819548872</v>
+        <v>46.938775510204</v>
       </c>
       <c r="N19" s="15">
-        <v>-1.470588235294</v>
+        <v>1.408450704225</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F20" s="14">
         <v>23</v>
       </c>
       <c r="G20" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H20" s="15">
-        <v>53.333333333333</v>
+        <v>27.777777777777</v>
       </c>
       <c r="I20" s="14">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J20" s="14">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="K20" s="15">
-        <v>-15.625</v>
+        <v>-18.309859154929</v>
       </c>
       <c r="L20" s="15">
-        <v>-40</v>
+        <v>-41.414141414141</v>
       </c>
       <c r="M20" s="15">
-        <v>22.727272727272</v>
+        <v>28.888888888888</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.329113924050</v>
+        <v>-86.352941176470</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D21" s="17">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E21" s="18">
-        <v>22.727272727272</v>
+        <v>12.195121951219</v>
       </c>
       <c r="F21" s="17">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G21" s="17">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="H21" s="18">
-        <v>2.020202020202</v>
+        <v>8.994708994709</v>
       </c>
       <c r="I21" s="17">
-        <v>650</v>
+        <v>698</v>
       </c>
       <c r="J21" s="17">
-        <v>657</v>
+        <v>698</v>
       </c>
       <c r="K21" s="18">
-        <v>-1.065449010654</v>
+        <v>0</v>
       </c>
       <c r="L21" s="18">
-        <v>-0.153609831029</v>
+        <v>0</v>
       </c>
       <c r="M21" s="18">
-        <v>27.952755905511</v>
+        <v>29.259259259259</v>
       </c>
       <c r="N21" s="18">
-        <v>-63.421496904895</v>
+        <v>-63.068783068783</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>2</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J22" s="14">
         <v>10</v>
       </c>
       <c r="K22" s="15">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="L22" s="15">
-        <v>-26.666666666666</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>266.666666666667</v>
+        <v>333.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1251,7 +1251,7 @@
         <v>200</v>
       </c>
       <c r="M23" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="D24" s="14">
         <v>38</v>
       </c>
       <c r="E24" s="15">
-        <v>-31.578947368421</v>
+        <v>63.157894736842</v>
       </c>
       <c r="F24" s="14">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="G24" s="14">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="H24" s="15">
-        <v>22.388059701492</v>
+        <v>21.527777777777</v>
       </c>
       <c r="I24" s="14">
-        <v>498</v>
+        <v>561</v>
       </c>
       <c r="J24" s="14">
-        <v>428</v>
+        <v>466</v>
       </c>
       <c r="K24" s="15">
-        <v>16.355140186915</v>
+        <v>20.386266094420</v>
       </c>
       <c r="L24" s="15">
-        <v>-4.780114722753</v>
+        <v>-1.058201058201</v>
       </c>
       <c r="M24" s="15">
-        <v>53.703703703703</v>
+        <v>58.474576271186</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="D25" s="14">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E25" s="15">
-        <v>20</v>
+        <v>168.75</v>
       </c>
       <c r="F25" s="14">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="G25" s="14">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="H25" s="15">
-        <v>79.245283018867</v>
+        <v>88.333333333333</v>
       </c>
       <c r="I25" s="14">
-        <v>282</v>
+        <v>325</v>
       </c>
       <c r="J25" s="14">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="K25" s="15">
-        <v>46.113989637305</v>
+        <v>55.502392344497</v>
       </c>
       <c r="L25" s="15">
-        <v>-9.615384615384</v>
+        <v>-4.970760233918</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D26" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E26" s="15">
-        <v>15</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="F26" s="14">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G26" s="14">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H26" s="15">
-        <v>-21.686746987951</v>
+        <v>-28.089887640449</v>
       </c>
       <c r="I26" s="14">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="J26" s="14">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="K26" s="15">
-        <v>21.287128712871</v>
+        <v>16.964285714285</v>
       </c>
       <c r="L26" s="15">
-        <v>10.859728506787</v>
+        <v>14.410480349345</v>
       </c>
       <c r="M26" s="15">
-        <v>20.689655172413</v>
+        <v>16.444444444444</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>2</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>100</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>33.333333333333</v>
+        <v>150</v>
       </c>
       <c r="I27" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J27" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K27" s="15">
-        <v>-33.333333333333</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="L27" s="15">
-        <v>-50</v>
+        <v>-44</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D28" s="14">
         <v>4</v>
       </c>
       <c r="E28" s="15">
-        <v>-75</v>
+        <v>25</v>
       </c>
       <c r="F28" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G28" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H28" s="15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J28" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K28" s="15">
-        <v>-8</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="L28" s="15">
-        <v>-17.857142857142</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>2</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,26 +1616,26 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="14">
         <v>2</v>
       </c>
       <c r="H33" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+        <v>-50</v>
+      </c>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="14">
         <v>2</v>
       </c>
       <c r="K33" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L33" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-052pct.xlsx
+++ b/data/source/weekly/cs-en-us-052pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J15" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K15" s="15">
-        <v>-44.444444444444</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="L15" s="15">
-        <v>-41.176470588235</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="M15" s="15">
-        <v>42.857142857142</v>
+        <v>71.428571428571</v>
       </c>
       <c r="N15" s="15">
-        <v>-44.444444444444</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E16" s="15">
-        <v>-11.111111111111</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="F16" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G16" s="14">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>-10.810810810810</v>
       </c>
       <c r="I16" s="14">
+        <v>123</v>
+      </c>
+      <c r="J16" s="14">
         <v>113</v>
       </c>
-      <c r="J16" s="14">
-        <v>102</v>
-      </c>
       <c r="K16" s="15">
-        <v>10.784313725490</v>
+        <v>8.849557522123</v>
       </c>
       <c r="L16" s="15">
-        <v>-20.979020979021</v>
+        <v>-20.645161290322</v>
       </c>
       <c r="M16" s="15">
-        <v>-5.042016806722</v>
+        <v>-8.208955223880</v>
       </c>
       <c r="N16" s="15">
-        <v>-73.781902552204</v>
+        <v>-73.144104803493</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E17" s="15">
-        <v>128.571428571429</v>
+        <v>78.571428571428</v>
       </c>
       <c r="F17" s="14">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G17" s="14">
+        <v>50</v>
+      </c>
+      <c r="H17" s="15">
         <v>56</v>
       </c>
-      <c r="H17" s="15">
-        <v>41.071428571428</v>
-      </c>
       <c r="I17" s="14">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="J17" s="14">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="K17" s="15">
-        <v>21.495327102803</v>
+        <v>24.561403508771</v>
       </c>
       <c r="L17" s="15">
-        <v>46.067415730337</v>
+        <v>49.473684210526</v>
       </c>
       <c r="M17" s="15">
-        <v>126.086956521739</v>
+        <v>123.622047244094</v>
       </c>
       <c r="N17" s="15">
-        <v>50.289017341040</v>
+        <v>55.191256830601</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
         <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F18" s="14">
         <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H18" s="15">
-        <v>-50</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="I18" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J18" s="14">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K18" s="15">
-        <v>-42.424242424242</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="L18" s="15">
-        <v>-26.923076923076</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="M18" s="15">
-        <v>-63.809523809523</v>
+        <v>-61.467889908256</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.831168831168</v>
+        <v>-93.703148425787</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D19" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E19" s="15">
-        <v>7.142857142857</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F19" s="14">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G19" s="14">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H19" s="15">
-        <v>-5</v>
+        <v>1.612903225806</v>
       </c>
       <c r="I19" s="14">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="J19" s="14">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="K19" s="15">
-        <v>-4.845814977973</v>
+        <v>-5.306122448979</v>
       </c>
       <c r="L19" s="15">
-        <v>3.846153846153</v>
+        <v>2.654867256637</v>
       </c>
       <c r="M19" s="15">
-        <v>46.938775510204</v>
+        <v>44.099378881987</v>
       </c>
       <c r="N19" s="15">
-        <v>1.408450704225</v>
+        <v>-1.276595744680</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-42.857142857142</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F20" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G20" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H20" s="15">
-        <v>27.777777777777</v>
+        <v>41.176470588235</v>
       </c>
       <c r="I20" s="14">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="J20" s="14">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K20" s="15">
-        <v>-18.309859154929</v>
+        <v>-10.810810810810</v>
       </c>
       <c r="L20" s="15">
-        <v>-41.414141414141</v>
+        <v>-38.317757009345</v>
       </c>
       <c r="M20" s="15">
-        <v>28.888888888888</v>
+        <v>34.693877551020</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.352941176470</v>
+        <v>-85.683297180043</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="D21" s="17">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E21" s="18">
-        <v>12.195121951219</v>
+        <v>28</v>
       </c>
       <c r="F21" s="17">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="G21" s="17">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="H21" s="18">
-        <v>8.994708994709</v>
+        <v>16.216216216216</v>
       </c>
       <c r="I21" s="17">
-        <v>698</v>
+        <v>762</v>
       </c>
       <c r="J21" s="17">
-        <v>698</v>
+        <v>748</v>
       </c>
       <c r="K21" s="18">
-        <v>0</v>
+        <v>1.871657754010</v>
       </c>
       <c r="L21" s="18">
-        <v>0</v>
+        <v>1.061007957559</v>
       </c>
       <c r="M21" s="18">
-        <v>29.259259259259</v>
+        <v>29.371816638370</v>
       </c>
       <c r="N21" s="18">
-        <v>-63.068783068783</v>
+        <v>-62.610402355250</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>2</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1207,10 +1207,10 @@
         <v>30</v>
       </c>
       <c r="L22" s="15">
-        <v>-13.333333333333</v>
+        <v>-18.75</v>
       </c>
       <c r="M22" s="15">
-        <v>333.333333333333</v>
+        <v>85.714285714285</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1248,7 +1248,7 @@
         <v>21</v>
       </c>
       <c r="L23" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="M23" s="15">
         <v>0</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D24" s="14">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E24" s="15">
-        <v>63.157894736842</v>
+        <v>17.647058823529</v>
       </c>
       <c r="F24" s="14">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="G24" s="14">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H24" s="15">
-        <v>21.527777777777</v>
+        <v>26.027397260274</v>
       </c>
       <c r="I24" s="14">
-        <v>561</v>
+        <v>602</v>
       </c>
       <c r="J24" s="14">
-        <v>466</v>
+        <v>500</v>
       </c>
       <c r="K24" s="15">
-        <v>20.386266094420</v>
+        <v>20.4</v>
       </c>
       <c r="L24" s="15">
-        <v>-1.058201058201</v>
+        <v>-0.660066006600</v>
       </c>
       <c r="M24" s="15">
-        <v>58.474576271186</v>
+        <v>57.591623036649</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="D25" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E25" s="15">
-        <v>168.75</v>
+        <v>6.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G25" s="14">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H25" s="15">
-        <v>88.333333333333</v>
+        <v>87.931034482758</v>
       </c>
       <c r="I25" s="14">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="J25" s="14">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="K25" s="15">
-        <v>55.502392344497</v>
+        <v>52.678571428571</v>
       </c>
       <c r="L25" s="15">
-        <v>-4.970760233918</v>
+        <v>-6.043956043956</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>18</v>
+      </c>
+      <c r="D26" s="14">
         <v>19</v>
       </c>
-      <c r="D26" s="14">
-        <v>22</v>
-      </c>
       <c r="E26" s="15">
-        <v>-13.636363636363</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="F26" s="14">
         <v>64</v>
       </c>
       <c r="G26" s="14">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H26" s="15">
-        <v>-28.089887640449</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="I26" s="14">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="J26" s="14">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="K26" s="15">
-        <v>16.964285714285</v>
+        <v>14.40329218107</v>
       </c>
       <c r="L26" s="15">
-        <v>14.410480349345</v>
+        <v>14.876033057851</v>
       </c>
       <c r="M26" s="15">
-        <v>16.444444444444</v>
+        <v>13.469387755102</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>100</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J27" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K27" s="15">
-        <v>-26.315789473684</v>
+        <v>-20</v>
       </c>
       <c r="L27" s="15">
-        <v>-44</v>
+        <v>-36</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F28" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I28" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J28" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K28" s="15">
-        <v>-3.448275862068</v>
+        <v>-6.25</v>
       </c>
       <c r="L28" s="15">
-        <v>-9.677419354838</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="14">
         <v>3</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>200</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
         <v>5</v>
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-66.666666666666</v>
+        <v>-68.75</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1519,11 +1519,11 @@
       <c r="F30" s="14">
         <v>2</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
         <v>4</v>
@@ -1541,7 +1541,7 @@
         <v>-20</v>
       </c>
       <c r="N30" s="15">
-        <v>-63.636363636363</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1620,10 +1620,10 @@
         <v>1</v>
       </c>
       <c r="G33" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-052pct.xlsx
+++ b/data/source/weekly/cs-en-us-052pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>2</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>100</v>
+        <v>4</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I15" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J15" s="14">
         <v>19</v>
       </c>
       <c r="K15" s="15">
-        <v>-36.842105263157</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="L15" s="15">
-        <v>-29.411764705882</v>
+        <v>-20</v>
       </c>
       <c r="M15" s="15">
-        <v>71.428571428571</v>
+        <v>128.571428571429</v>
       </c>
       <c r="N15" s="15">
-        <v>-40</v>
+        <v>-27.272727272727</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E16" s="15">
-        <v>-18.181818181818</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G16" s="14">
         <v>37</v>
       </c>
       <c r="H16" s="15">
-        <v>-10.810810810810</v>
+        <v>-2.702702702702</v>
       </c>
       <c r="I16" s="14">
+        <v>132</v>
+      </c>
+      <c r="J16" s="14">
         <v>123</v>
       </c>
-      <c r="J16" s="14">
-        <v>113</v>
-      </c>
       <c r="K16" s="15">
-        <v>8.849557522123</v>
+        <v>7.317073170731</v>
       </c>
       <c r="L16" s="15">
-        <v>-20.645161290322</v>
+        <v>-19.018404907975</v>
       </c>
       <c r="M16" s="15">
-        <v>-8.208955223880</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="N16" s="15">
-        <v>-73.144104803493</v>
+        <v>-73.279352226720</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D17" s="14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E17" s="15">
-        <v>78.571428571428</v>
+        <v>-15</v>
       </c>
       <c r="F17" s="14">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G17" s="14">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H17" s="15">
-        <v>56</v>
+        <v>77.551020408163</v>
       </c>
       <c r="I17" s="14">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="J17" s="14">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="K17" s="15">
-        <v>24.561403508771</v>
+        <v>22.580645161290</v>
       </c>
       <c r="L17" s="15">
-        <v>49.473684210526</v>
+        <v>47.572815533980</v>
       </c>
       <c r="M17" s="15">
-        <v>123.622047244094</v>
+        <v>121.897810218978</v>
       </c>
       <c r="N17" s="15">
-        <v>55.191256830601</v>
+        <v>60.846560846560</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>33.333333333333</v>
+        <v>350</v>
       </c>
       <c r="F18" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G18" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>-35.294117647058</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I18" s="14">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="J18" s="14">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K18" s="15">
-        <v>-39.130434782608</v>
+        <v>-26.760563380281</v>
       </c>
       <c r="L18" s="15">
-        <v>-27.586206896551</v>
+        <v>-18.75</v>
       </c>
       <c r="M18" s="15">
-        <v>-61.467889908256</v>
+        <v>-54.385964912280</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.703148425787</v>
+        <v>-92.634560906515</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E19" s="15">
-        <v>-11.111111111111</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="F19" s="14">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="G19" s="14">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="H19" s="15">
-        <v>1.612903225806</v>
+        <v>-19.117647058823</v>
       </c>
       <c r="I19" s="14">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="J19" s="14">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="K19" s="15">
-        <v>-5.306122448979</v>
+        <v>-7.954545454545</v>
       </c>
       <c r="L19" s="15">
-        <v>2.654867256637</v>
+        <v>2.531645569620</v>
       </c>
       <c r="M19" s="15">
-        <v>44.099378881987</v>
+        <v>42.105263157894</v>
       </c>
       <c r="N19" s="15">
-        <v>-1.276595744680</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E20" s="15">
-        <v>166.666666666667</v>
+        <v>-80</v>
       </c>
       <c r="F20" s="14">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G20" s="14">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H20" s="15">
-        <v>41.176470588235</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="I20" s="14">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J20" s="14">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K20" s="15">
-        <v>-10.810810810810</v>
+        <v>-20.238095238095</v>
       </c>
       <c r="L20" s="15">
-        <v>-38.317757009345</v>
+        <v>-39.639639639639</v>
       </c>
       <c r="M20" s="15">
-        <v>34.693877551020</v>
+        <v>34</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.683297180043</v>
+        <v>-86.270491803278</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="D21" s="17">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E21" s="18">
-        <v>28</v>
+        <v>-13.114754098360</v>
       </c>
       <c r="F21" s="17">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G21" s="17">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="H21" s="18">
-        <v>16.216216216216</v>
+        <v>11.734693877551</v>
       </c>
       <c r="I21" s="17">
-        <v>762</v>
+        <v>817</v>
       </c>
       <c r="J21" s="17">
-        <v>748</v>
+        <v>809</v>
       </c>
       <c r="K21" s="18">
-        <v>1.871657754010</v>
+        <v>0.988875154511</v>
       </c>
       <c r="L21" s="18">
-        <v>1.061007957559</v>
+        <v>1.870324189526</v>
       </c>
       <c r="M21" s="18">
-        <v>29.371816638370</v>
+        <v>30.72</v>
       </c>
       <c r="N21" s="18">
-        <v>-62.610402355250</v>
+        <v>-62.228386500231</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>0</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>200</v>
       </c>
       <c r="I22" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J22" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K22" s="15">
-        <v>30</v>
+        <v>27.272727272727</v>
       </c>
       <c r="L22" s="15">
-        <v>-18.75</v>
+        <v>-12.5</v>
       </c>
       <c r="M22" s="15">
-        <v>85.714285714285</v>
+        <v>75</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D24" s="14">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E24" s="15">
-        <v>17.647058823529</v>
+        <v>9.523809523809</v>
       </c>
       <c r="F24" s="14">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="G24" s="14">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="H24" s="15">
-        <v>26.027397260274</v>
+        <v>14.473684210526</v>
       </c>
       <c r="I24" s="14">
-        <v>602</v>
+        <v>646</v>
       </c>
       <c r="J24" s="14">
-        <v>500</v>
+        <v>542</v>
       </c>
       <c r="K24" s="15">
-        <v>20.4</v>
+        <v>19.188191881918</v>
       </c>
       <c r="L24" s="15">
-        <v>-0.660066006600</v>
+        <v>1.412872841444</v>
       </c>
       <c r="M24" s="15">
-        <v>57.591623036649</v>
+        <v>57.946210268948</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D25" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E25" s="15">
-        <v>6.666666666666</v>
+        <v>31.578947368421</v>
       </c>
       <c r="F25" s="14">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="G25" s="14">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H25" s="15">
-        <v>87.931034482758</v>
+        <v>60</v>
       </c>
       <c r="I25" s="14">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="J25" s="14">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="K25" s="15">
-        <v>52.678571428571</v>
+        <v>50.617283950617</v>
       </c>
       <c r="L25" s="15">
-        <v>-6.043956043956</v>
+        <v>-1.612903225806</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D26" s="14">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E26" s="15">
-        <v>-5.263157894736</v>
+        <v>-32</v>
       </c>
       <c r="F26" s="14">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="G26" s="14">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H26" s="15">
-        <v>-23.809523809523</v>
+        <v>-15.116279069767</v>
       </c>
       <c r="I26" s="14">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="J26" s="14">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="K26" s="15">
-        <v>14.40329218107</v>
+        <v>9.701492537313</v>
       </c>
       <c r="L26" s="15">
-        <v>14.876033057851</v>
+        <v>13.513513513513</v>
       </c>
       <c r="M26" s="15">
-        <v>13.469387755102</v>
+        <v>9.701492537313</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>100</v>
+        <v>5</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>450</v>
       </c>
       <c r="I27" s="14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J27" s="14">
         <v>20</v>
       </c>
       <c r="K27" s="15">
-        <v>-20</v>
+        <v>5</v>
       </c>
       <c r="L27" s="15">
-        <v>-36</v>
+        <v>-25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="F28" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G28" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H28" s="15">
-        <v>-9.090909090909</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J28" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K28" s="15">
-        <v>-6.25</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L28" s="15">
-        <v>-14.285714285714</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1476,7 +1476,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1497,7 +1497,7 @@
         <v>-54.545454545454</v>
       </c>
       <c r="M29" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N29" s="15">
         <v>-68.75</v>
@@ -1517,7 +1517,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1538,7 +1538,7 @@
         <v>-42.857142857142</v>
       </c>
       <c r="M30" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N30" s="15">
         <v>-66.666666666666</v>
@@ -1619,11 +1619,11 @@
       <c r="F33" s="14">
         <v>1</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>0</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-052pct.xlsx
+++ b/data/source/weekly/cs-en-us-052pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -854,29 +854,29 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>3</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
+        <v>200</v>
       </c>
       <c r="L14" s="15">
         <v>200</v>
@@ -885,21 +885,21 @@
         <v>50</v>
       </c>
       <c r="N14" s="15">
-        <v>-78.571428571428</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F15" s="14">
         <v>8</v>
@@ -911,22 +911,22 @@
         <v>300</v>
       </c>
       <c r="I15" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J15" s="14">
         <v>19</v>
       </c>
       <c r="K15" s="15">
-        <v>-15.789473684210</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="L15" s="15">
-        <v>-20</v>
+        <v>-15</v>
       </c>
       <c r="M15" s="15">
-        <v>128.571428571429</v>
+        <v>112.5</v>
       </c>
       <c r="N15" s="15">
-        <v>-27.272727272727</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D16" s="14">
         <v>10</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F16" s="14">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G16" s="14">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H16" s="15">
-        <v>-2.702702702702</v>
+        <v>5</v>
       </c>
       <c r="I16" s="14">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="J16" s="14">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="K16" s="15">
-        <v>7.317073170731</v>
+        <v>9.774436090225</v>
       </c>
       <c r="L16" s="15">
-        <v>-19.018404907975</v>
+        <v>-15.116279069767</v>
       </c>
       <c r="M16" s="15">
-        <v>-8.333333333333</v>
+        <v>-7.006369426751</v>
       </c>
       <c r="N16" s="15">
-        <v>-73.279352226720</v>
+        <v>-72.137404580152</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D17" s="14">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E17" s="15">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="G17" s="14">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H17" s="15">
-        <v>77.551020408163</v>
+        <v>32.727272727272</v>
       </c>
       <c r="I17" s="14">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="J17" s="14">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="K17" s="15">
-        <v>22.580645161290</v>
+        <v>21.374045801526</v>
       </c>
       <c r="L17" s="15">
-        <v>47.572815533980</v>
+        <v>41.964285714285</v>
       </c>
       <c r="M17" s="15">
-        <v>121.897810218978</v>
+        <v>120.833333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>60.846560846560</v>
+        <v>56.650246305418</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>350</v>
+        <v>25</v>
       </c>
       <c r="F18" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G18" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>14.285714285714</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J18" s="14">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K18" s="15">
-        <v>-26.760563380281</v>
+        <v>-24</v>
       </c>
       <c r="L18" s="15">
-        <v>-18.75</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="M18" s="15">
-        <v>-54.385964912280</v>
+        <v>-52.5</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.634560906515</v>
+        <v>-92.389853137516</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D19" s="14">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E19" s="15">
-        <v>-42.105263157894</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="F19" s="14">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G19" s="14">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="H19" s="15">
-        <v>-19.117647058823</v>
+        <v>-20.779220779220</v>
       </c>
       <c r="I19" s="14">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="J19" s="14">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="K19" s="15">
-        <v>-7.954545454545</v>
+        <v>-9.655172413793</v>
       </c>
       <c r="L19" s="15">
-        <v>2.531645569620</v>
+        <v>4.382470119521</v>
       </c>
       <c r="M19" s="15">
-        <v>42.105263157894</v>
+        <v>43.956043956044</v>
       </c>
       <c r="N19" s="15">
-        <v>-2.8</v>
+        <v>-2.962962962962</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G20" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H20" s="15">
-        <v>-34.615384615384</v>
+        <v>-25.925925925925</v>
       </c>
       <c r="I20" s="14">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="J20" s="14">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K20" s="15">
-        <v>-20.238095238095</v>
+        <v>-18.681318681318</v>
       </c>
       <c r="L20" s="15">
-        <v>-39.639639639639</v>
+        <v>-37.815126050420</v>
       </c>
       <c r="M20" s="15">
-        <v>34</v>
+        <v>39.622641509434</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.270491803278</v>
+        <v>-85.658914728682</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D21" s="17">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E21" s="18">
-        <v>-13.114754098360</v>
+        <v>-6.451612903225</v>
       </c>
       <c r="F21" s="17">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G21" s="17">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="H21" s="18">
-        <v>11.734693877551</v>
+        <v>4.672897196261</v>
       </c>
       <c r="I21" s="17">
-        <v>817</v>
+        <v>877</v>
       </c>
       <c r="J21" s="17">
-        <v>809</v>
+        <v>871</v>
       </c>
       <c r="K21" s="18">
-        <v>0.988875154511</v>
+        <v>0.688863375430</v>
       </c>
       <c r="L21" s="18">
-        <v>1.870324189526</v>
+        <v>2.813599062133</v>
       </c>
       <c r="M21" s="18">
-        <v>30.72</v>
+        <v>31.681681681681</v>
       </c>
       <c r="N21" s="18">
-        <v>-62.228386500231</v>
+        <v>-61.902693310165</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
-      </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>0</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="F22" s="14">
         <v>3</v>
@@ -1207,13 +1207,13 @@
         <v>27.272727272727</v>
       </c>
       <c r="L22" s="15">
-        <v>-12.5</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M22" s="15">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1227,7 +1227,7 @@
         <v>20</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
@@ -1236,7 +1236,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I23" s="14">
         <v>3</v>
@@ -1245,16 +1245,16 @@
         <v>20</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L23" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M23" s="15">
         <v>0</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D24" s="14">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="E24" s="15">
-        <v>9.523809523809</v>
+        <v>24.137931034482</v>
       </c>
       <c r="F24" s="14">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="G24" s="14">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="H24" s="15">
-        <v>14.473684210526</v>
+        <v>27.972027972028</v>
       </c>
       <c r="I24" s="14">
-        <v>646</v>
+        <v>682</v>
       </c>
       <c r="J24" s="14">
-        <v>542</v>
+        <v>571</v>
       </c>
       <c r="K24" s="15">
-        <v>19.188191881918</v>
+        <v>19.439579684763</v>
       </c>
       <c r="L24" s="15">
-        <v>1.412872841444</v>
+        <v>1.037037037037</v>
       </c>
       <c r="M24" s="15">
-        <v>57.946210268948</v>
+        <v>58.236658932714</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D25" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E25" s="15">
-        <v>31.578947368421</v>
+        <v>71.428571428571</v>
       </c>
       <c r="F25" s="14">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="G25" s="14">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H25" s="15">
-        <v>60</v>
+        <v>70.3125</v>
       </c>
       <c r="I25" s="14">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="J25" s="14">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="K25" s="15">
-        <v>50.617283950617</v>
+        <v>51.750972762645</v>
       </c>
       <c r="L25" s="15">
-        <v>-1.612903225806</v>
+        <v>-0.763358778625</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D26" s="14">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E26" s="15">
-        <v>-32</v>
+        <v>7.142857142857</v>
       </c>
       <c r="F26" s="14">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G26" s="14">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H26" s="15">
-        <v>-15.116279069767</v>
+        <v>-18.75</v>
       </c>
       <c r="I26" s="14">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="J26" s="14">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="K26" s="15">
-        <v>9.701492537313</v>
+        <v>9.219858156028</v>
       </c>
       <c r="L26" s="15">
-        <v>13.513513513513</v>
+        <v>13.235294117647</v>
       </c>
       <c r="M26" s="15">
-        <v>9.701492537313</v>
+        <v>6.574394463667</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,22 +1385,22 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F27" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="I27" s="14">
         <v>21</v>
@@ -1415,51 +1415,51 @@
         <v>-25</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>3</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E28" s="15">
-        <v>-25</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H28" s="15">
-        <v>-26.666666666666</v>
+        <v>-37.5</v>
       </c>
       <c r="I28" s="14">
         <v>32</v>
       </c>
       <c r="J28" s="14">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="K28" s="15">
-        <v>-11.111111111111</v>
+        <v>-21.951219512195</v>
       </c>
       <c r="L28" s="15">
-        <v>-15.789473684210</v>
+        <v>-21.951219512195</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1473,16 +1473,16 @@
         <v>20</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="14">
-        <v>2</v>
+        <v>22</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I29" s="14">
         <v>5</v>
@@ -1500,7 +1500,7 @@
         <v>-16.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-68.75</v>
+        <v>-73.684210526315</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1514,16 +1514,16 @@
         <v>20</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="14">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I30" s="14">
         <v>4</v>
@@ -1541,7 +1541,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-66.666666666666</v>
+        <v>-73.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I31" s="14">
         <v>2</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="L31" s="15">
+        <v>100</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1638,10 +1638,10 @@
         <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>51</v>

--- a/data/source/weekly/cs-en-us-052pct.xlsx
+++ b/data/source/weekly/cs-en-us-052pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
         <v>1</v>
@@ -899,34 +899,34 @@
         <v>20</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>8</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="I15" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J15" s="14">
         <v>19</v>
       </c>
       <c r="K15" s="15">
-        <v>-10.526315789473</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="L15" s="15">
-        <v>-15</v>
+        <v>-10</v>
       </c>
       <c r="M15" s="15">
-        <v>112.5</v>
+        <v>50</v>
       </c>
       <c r="N15" s="15">
-        <v>-32</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D16" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
         <v>42</v>
@@ -952,22 +952,22 @@
         <v>5</v>
       </c>
       <c r="I16" s="14">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="J16" s="14">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="K16" s="15">
-        <v>9.774436090225</v>
+        <v>9.154929577464</v>
       </c>
       <c r="L16" s="15">
-        <v>-15.116279069767</v>
+        <v>-13.888888888888</v>
       </c>
       <c r="M16" s="15">
-        <v>-7.006369426751</v>
+        <v>-9.356725146198</v>
       </c>
       <c r="N16" s="15">
-        <v>-72.137404580152</v>
+        <v>-71.971066907775</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D17" s="14">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F17" s="14">
         <v>73</v>
       </c>
       <c r="G17" s="14">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H17" s="15">
-        <v>32.727272727272</v>
+        <v>5.797101449275</v>
       </c>
       <c r="I17" s="14">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="J17" s="14">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="K17" s="15">
-        <v>21.374045801526</v>
+        <v>18.374558303886</v>
       </c>
       <c r="L17" s="15">
-        <v>41.964285714285</v>
+        <v>38.429752066115</v>
       </c>
       <c r="M17" s="15">
-        <v>120.833333333333</v>
+        <v>118.954248366013</v>
       </c>
       <c r="N17" s="15">
-        <v>56.650246305418</v>
+        <v>58.018867924528</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>66.666666666666</v>
+        <v>90.909090909090</v>
       </c>
       <c r="I18" s="14">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J18" s="14">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K18" s="15">
-        <v>-24</v>
+        <v>-22.077922077922</v>
       </c>
       <c r="L18" s="15">
-        <v>-13.636363636363</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="M18" s="15">
-        <v>-52.5</v>
+        <v>-52.755905511811</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.389853137516</v>
+        <v>-92.583436341161</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>16</v>
+      </c>
+      <c r="D19" s="14">
         <v>19</v>
       </c>
-      <c r="D19" s="14">
-        <v>26</v>
-      </c>
       <c r="E19" s="15">
-        <v>-26.923076923076</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="F19" s="14">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G19" s="14">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H19" s="15">
-        <v>-20.779220779220</v>
+        <v>-23.170731707317</v>
       </c>
       <c r="I19" s="14">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="J19" s="14">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="K19" s="15">
-        <v>-9.655172413793</v>
+        <v>-9.708737864077</v>
       </c>
       <c r="L19" s="15">
-        <v>4.382470119521</v>
+        <v>4.104477611940</v>
       </c>
       <c r="M19" s="15">
-        <v>43.956043956044</v>
+        <v>48.404255319148</v>
       </c>
       <c r="N19" s="15">
-        <v>-2.962962962962</v>
+        <v>-1.063829787234</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
         <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G20" s="14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H20" s="15">
-        <v>-25.925925925925</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I20" s="14">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="J20" s="14">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="K20" s="15">
-        <v>-18.681318681318</v>
+        <v>-17.525773195876</v>
       </c>
       <c r="L20" s="15">
-        <v>-37.815126050420</v>
+        <v>-37.007874015748</v>
       </c>
       <c r="M20" s="15">
-        <v>39.622641509434</v>
+        <v>31.147540983606</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.658914728682</v>
+        <v>-85.533453887884</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D21" s="17">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E21" s="18">
-        <v>-6.451612903225</v>
+        <v>-7.017543859649</v>
       </c>
       <c r="F21" s="17">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="G21" s="17">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="H21" s="18">
-        <v>4.672897196261</v>
+        <v>-0.434782608695</v>
       </c>
       <c r="I21" s="17">
-        <v>877</v>
+        <v>930</v>
       </c>
       <c r="J21" s="17">
-        <v>871</v>
+        <v>928</v>
       </c>
       <c r="K21" s="18">
-        <v>0.688863375430</v>
+        <v>0.215517241379</v>
       </c>
       <c r="L21" s="18">
-        <v>2.813599062133</v>
+        <v>2.649006622516</v>
       </c>
       <c r="M21" s="18">
-        <v>31.681681681681</v>
+        <v>30.252100840336</v>
       </c>
       <c r="N21" s="18">
-        <v>-61.902693310165</v>
+        <v>-62.056303549571</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,38 +1182,38 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>22</v>
+      <c r="D22" s="14">
+        <v>4</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>200</v>
+        <v>-80</v>
       </c>
       <c r="I22" s="14">
         <v>14</v>
       </c>
       <c r="J22" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K22" s="15">
-        <v>27.272727272727</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L22" s="15">
-        <v>-22.222222222222</v>
+        <v>-30</v>
       </c>
       <c r="M22" s="15">
         <v>40</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1227,7 +1227,7 @@
         <v>20</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
@@ -1236,7 +1236,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I23" s="14">
         <v>3</v>
@@ -1245,16 +1245,16 @@
         <v>20</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L23" s="15">
         <v>0</v>
       </c>
       <c r="M23" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D24" s="14">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E24" s="15">
-        <v>24.137931034482</v>
+        <v>86.956521739130</v>
       </c>
       <c r="F24" s="14">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="G24" s="14">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="H24" s="15">
-        <v>27.972027972028</v>
+        <v>28.125</v>
       </c>
       <c r="I24" s="14">
-        <v>682</v>
+        <v>726</v>
       </c>
       <c r="J24" s="14">
-        <v>571</v>
+        <v>594</v>
       </c>
       <c r="K24" s="15">
-        <v>19.439579684763</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L24" s="15">
-        <v>1.037037037037</v>
+        <v>3.418803418803</v>
       </c>
       <c r="M24" s="15">
-        <v>58.236658932714</v>
+        <v>57.483731019522</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D25" s="14">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>71.428571428571</v>
+        <v>175</v>
       </c>
       <c r="F25" s="14">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="G25" s="14">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="H25" s="15">
-        <v>70.3125</v>
+        <v>55.357142857142</v>
       </c>
       <c r="I25" s="14">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="J25" s="14">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="K25" s="15">
-        <v>51.750972762645</v>
+        <v>55.471698113207</v>
       </c>
       <c r="L25" s="15">
-        <v>-0.763358778625</v>
+        <v>2.743142144638</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D26" s="14">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E26" s="15">
-        <v>7.142857142857</v>
+        <v>43.478260869565</v>
       </c>
       <c r="F26" s="14">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="G26" s="14">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H26" s="15">
-        <v>-18.75</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14">
-        <v>308</v>
+        <v>341</v>
       </c>
       <c r="J26" s="14">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="K26" s="15">
-        <v>9.219858156028</v>
+        <v>11.803278688524</v>
       </c>
       <c r="L26" s="15">
-        <v>13.235294117647</v>
+        <v>19.230769230769</v>
       </c>
       <c r="M26" s="15">
-        <v>6.574394463667</v>
+        <v>12.171052631578</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1387,79 +1387,79 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>22</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="I27" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J27" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K27" s="15">
-        <v>5</v>
+        <v>4.761904761904</v>
       </c>
       <c r="L27" s="15">
-        <v>-25</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F28" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H28" s="15">
-        <v>-37.5</v>
+        <v>-63.157894736842</v>
       </c>
       <c r="I28" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J28" s="14">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="K28" s="15">
-        <v>-21.951219512195</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>-21.951219512195</v>
+        <v>-17.073170731707</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1469,38 +1469,38 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>22</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>22</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>5</v>
       </c>
       <c r="J29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L29" s="15">
         <v>-54.545454545454</v>
       </c>
       <c r="M29" s="15">
-        <v>-16.666666666666</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="N29" s="15">
-        <v>-73.684210526315</v>
+        <v>-76.190476190476</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,38 +1510,38 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>22</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>22</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>4</v>
       </c>
       <c r="J30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L30" s="15">
         <v>-42.857142857142</v>
       </c>
       <c r="M30" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="N30" s="15">
-        <v>-73.333333333333</v>
+        <v>-76.470588235294</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>2</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L31" s="15">
         <v>100</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,16 +1614,16 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F33" s="14">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1638,10 +1638,10 @@
         <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>51</v>
